--- a/Analysis/03_Hypothesis_Tests/1_merged_index_panel.xlsx
+++ b/Analysis/03_Hypothesis_Tests/1_merged_index_panel.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ63"/>
+  <dimension ref="A1:AP63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,170 +464,165 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>SNII_DIM_size_controlled</t>
+          <t>EIPI_CH</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>EIPI_CH</t>
+          <t>EIPI_CH_size_controlled</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>EIPI_CH_size_controlled</t>
+          <t>EIPI_TOPSIS_size_controlled</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>EIPI_TOPSIS_size_controlled</t>
+          <t>EIPI_PCA_size_controlled</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>EIPI_PCA_size_controlled</t>
+          <t>EIPI_AVG_size_controlled</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>EIPI_AVG_size_controlled</t>
+          <t>C1_growth_spillover</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>C1_growth_spillover</t>
+          <t>C2_welfare_distribution</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>C2_welfare_distribution</t>
+          <t>C3_external_balance</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>C3_external_balance</t>
+          <t>C4_price_stability</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>C4_price_stability</t>
+          <t>backward_linkage</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>backward_linkage</t>
+          <t>forward_linkage</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>forward_linkage</t>
+          <t>eigenvector_centrality</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>eigenvector_centrality</t>
+          <t>pagerank</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>pagerank</t>
+          <t>betweenness_centrality</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>betweenness_centrality</t>
+          <t>hub_score</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>hub_score</t>
+          <t>authority_score</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>authority_score</t>
+          <t>GDP_pct_change</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>GDP_pct_change</t>
+          <t>Welfare_pct_change</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Welfare_pct_change</t>
+          <t>ExportShare_pct_change</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>ExportShare_pct_change</t>
+          <t>LaborIncomeShare_pct_change</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>LaborIncomeShare_pct_change</t>
+          <t>Spillover_pct_change</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Spillover_pct_change</t>
+          <t>ImportDependency_pct_change</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>ImportDependency_pct_change</t>
+          <t>CPI_pct_change</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>CPI_pct_change</t>
+          <t>GDP_base</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>GDP_base</t>
+          <t>Welfare_base</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Welfare_base</t>
+          <t>ExportShare_base</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>ExportShare_base</t>
+          <t>LaborIncomeShare_base</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>LaborIncomeShare_base</t>
+          <t>Spillover_base</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>Spillover_base</t>
+          <t>ImportDependency_base</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>ImportDependency_base</t>
+          <t>CPI_base</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>CPI_base</t>
+          <t>total_output</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>total_output</t>
+          <t>domar_weight</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
-        <is>
-          <t>domar_weight</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
         <is>
           <t>log_output</t>
         </is>
@@ -664,105 +659,102 @@
         <v>0.2917221279913814</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1780322661831668</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9904446051399636</v>
+        <v>0.9266532090109549</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9003539144670568</v>
+        <v>0.8097003993816735</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8423614871417641</v>
+        <v>0.9178489733153056</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8995212246499882</v>
+        <v>0.6948302469776479</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6948302469776479</v>
+        <v>0.970900284109632</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.970900284109632</v>
+        <v>0.650794257218719</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5990786900588778</v>
+        <v>0.9241259782121448</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9241259782121449</v>
+        <v>0.264275065432829</v>
       </c>
       <c r="T2" t="n">
-        <v>0.264275065432829</v>
+        <v>0.3991224221957245</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3991224221957245</v>
+        <v>0.1612604724436165</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1612604724436165</v>
+        <v>0.05899917058805625</v>
       </c>
       <c r="W2" t="n">
-        <v>0.05899917058805625</v>
+        <v>0.01888888888888889</v>
       </c>
       <c r="X2" t="n">
-        <v>0.01888888888888889</v>
+        <v>0.299392555367483</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.299392555367483</v>
+        <v>0.1547126688851078</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1547126688851078</v>
+        <v>0.6167452952044618</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.6167452952044618</v>
+        <v>0.6380199568466669</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6380199568466669</v>
+        <v>-0.2998714584562907</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.2998714584562907</v>
+        <v>0.1891156375004895</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.1891156375004895</v>
+        <v>0.1879200548187051</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1879200548187051</v>
+        <v>-0.3951176902621632</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.3465983102620257</v>
+        <v>-0.2892668444583677</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.2892668444583677</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH2" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM2" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>100</v>
+        <v>2865.510018704435</v>
       </c>
       <c r="AO2" t="n">
-        <v>2865.510018704435</v>
+        <v>0.04728432193104235</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.04728432193104235</v>
-      </c>
-      <c r="AQ2" t="n">
         <v>7.960501630305497</v>
       </c>
     </row>
@@ -797,105 +789,102 @@
         <v>0.06377297465258534</v>
       </c>
       <c r="J3" t="n">
-        <v>0.365816322811453</v>
+        <v>0.01304944363710139</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01359138848836977</v>
+        <v>0.4249839345544715</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4356857864518975</v>
+        <v>0.4777217108720155</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4717221431873859</v>
+        <v>0.4496672482920687</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4391764224335984</v>
+        <v>0.4298902597192675</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4167485892118711</v>
+        <v>0.04239782507949155</v>
       </c>
       <c r="P3" t="n">
-        <v>0.04239782507949156</v>
+        <v>0.06089013334697349</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06089013334697348</v>
+        <v>0.3339914434384297</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3862968150312398</v>
+        <v>0.47039053475466</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4703905347546599</v>
+        <v>0.09978363111580127</v>
       </c>
       <c r="T3" t="n">
-        <v>0.09978363111580127</v>
+        <v>0.6817786201737066</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6817786201737066</v>
+        <v>0.1461794889121534</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1461794889121534</v>
+        <v>0.132303571714101</v>
       </c>
       <c r="W3" t="n">
-        <v>0.132303571714101</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01666666666666667</v>
+        <v>0.06206787019470198</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.06206787019470198</v>
+        <v>0.08591525304569098</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08591525304569098</v>
+        <v>0.02251247635338224</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.02251247635338224</v>
+        <v>0.01883837098686134</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01883837098686134</v>
+        <v>-0.01695207850797079</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.01695207850797079</v>
+        <v>0.02337534264310476</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02337534264310476</v>
+        <v>0.01828309829738651</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01828309829738651</v>
+        <v>0.001946199801281802</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0006164550708251039</v>
+        <v>0.004142268389244919</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.004142268389244919</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH3" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM3" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>100</v>
+        <v>69.43571329015894</v>
       </c>
       <c r="AO3" t="n">
-        <v>69.43571329015894</v>
+        <v>0.001145771816986302</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.001145771816986302</v>
-      </c>
-      <c r="AQ3" t="n">
         <v>4.240401335873965</v>
       </c>
     </row>
@@ -930,105 +919,102 @@
         <v>0.05498348604948911</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1619154483536985</v>
+        <v>0.005337086976234392</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003692339699757447</v>
+        <v>0.4184397474306021</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4267791127204308</v>
+        <v>0.4735609359520173</v>
       </c>
       <c r="M4" t="n">
-        <v>0.465963475536688</v>
+        <v>0.4153782909205798</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4098965625425127</v>
+        <v>0.4124154715678632</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3994197104505816</v>
+        <v>0.01028019879276019</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01028019879276019</v>
+        <v>0.05030183092567809</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05030183092567807</v>
+        <v>0.3575518950083084</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4057193439968776</v>
+        <v>0.4713053314122678</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4713053314122678</v>
+        <v>0.2140728661451473</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2140728661451473</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.2933414071421837</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2933414071421837</v>
+        <v>0.1467503369434669</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1467503369434669</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.2317624543981498</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2317624543981498</v>
+        <v>0.01792616514987679</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01792616514987679</v>
+        <v>0.004444554694778485</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.004444554694778485</v>
+        <v>0.02181645576775128</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02181645576775128</v>
+        <v>-0.01069578672414536</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.01069578672414536</v>
+        <v>-0.00613649798261512</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.00613649798261512</v>
+        <v>-0.007660333318897475</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.003020500195547004</v>
+        <v>0.003550712936359446</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.003550712936359446</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH4" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM4" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>69.26141076434305</v>
       </c>
       <c r="AO4" t="n">
-        <v>69.26141076434305</v>
+        <v>0.001142895618093164</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001142895618093164</v>
-      </c>
-      <c r="AQ4" t="n">
         <v>4.237887907873716</v>
       </c>
     </row>
@@ -1063,105 +1049,102 @@
         <v>0.3985755571019023</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4066946585817457</v>
+        <v>0.05887950811108643</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05690451593893761</v>
+        <v>0.1846218812499254</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1780530787239071</v>
+        <v>0.2064945890433726</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2025742547036805</v>
+        <v>0.2455622051035936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2561234574211091</v>
+        <v>0.1791144047537774</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1740608658788663</v>
+        <v>0.2060184721967299</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2060184721967299</v>
+        <v>0.1263193957937011</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1263193957937011</v>
+        <v>0.3374553807745517</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3792998473918334</v>
+        <v>0.3462110528959643</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3462110528959643</v>
+        <v>0.1303298803831925</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1303298803831925</v>
+        <v>0.9874031313836578</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9874031313836578</v>
+        <v>0.1442937411880311</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1442937411880311</v>
+        <v>0.08304200295155745</v>
       </c>
       <c r="W5" t="n">
-        <v>0.08304200295155745</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.4138920656938017</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4138920656938017</v>
+        <v>0.133292359449681</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.133292359449681</v>
+        <v>0.1119753299530532</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1119753299530532</v>
+        <v>0.07409887137586461</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07409887137586461</v>
+        <v>-0.0511495705449866</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0511495705449866</v>
+        <v>0.01000157693510133</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.01000157693510133</v>
+        <v>0.09559609691327986</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09559609691327986</v>
+        <v>-0.01009057463754874</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.005308152266032843</v>
+        <v>0.08444322819171646</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.08444322819171646</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH5" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM5" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>100</v>
+        <v>1526.026343486239</v>
       </c>
       <c r="AO5" t="n">
-        <v>1526.026343486239</v>
+        <v>0.02518124886308326</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.02518124886308326</v>
-      </c>
-      <c r="AQ5" t="n">
         <v>7.330422474792539</v>
       </c>
     </row>
@@ -1196,105 +1179,102 @@
         <v>0.2784209986117325</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3767537769622795</v>
+        <v>0.6373912342094957</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6645935384140625</v>
+        <v>0.5903679542265067</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6079501653753897</v>
+        <v>0.4758145086530895</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4671588285817264</v>
+        <v>0.4422044593446146</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4859348661744049</v>
+        <v>0.4859496108351066</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4927195001585572</v>
+        <v>0.4962382519789826</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4962382519789826</v>
+        <v>0.5550456384326018</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5550456384326018</v>
+        <v>0.4155921123262515</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4631125240633031</v>
+        <v>0.9166302048269642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9166302048269644</v>
+        <v>0.6058894750019067</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6058894750019067</v>
+        <v>0.2056573267435533</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2056573267435533</v>
+        <v>0.5135469203951822</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5135469203951822</v>
+        <v>0.3082732041611794</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3082732041611794</v>
+        <v>0.3455555555555556</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3455555555555556</v>
+        <v>0.2586921363968727</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.2586921363968727</v>
+        <v>0.5127168221774284</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.5127168221774284</v>
+        <v>0.3270864505753256</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.3270864505753256</v>
+        <v>0.3550193703679465</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.3550193703679465</v>
+        <v>0.04549460072468776</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04549460072468776</v>
+        <v>-0.07666470389888014</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.07666470389888014</v>
+        <v>0.1852365487914815</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1852365487914815</v>
+        <v>-0.05008363776153799</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0465771300344629</v>
+        <v>-0.2844196846193796</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.2844196846193796</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH6" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM6" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>100</v>
+        <v>3114.057519659189</v>
       </c>
       <c r="AO6" t="n">
-        <v>3114.057519659189</v>
+        <v>0.0513856511790951</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0513856511790951</v>
-      </c>
-      <c r="AQ6" t="n">
         <v>8.043681823533303</v>
       </c>
     </row>
@@ -1329,105 +1309,102 @@
         <v>0.1650545403371076</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1639591844006686</v>
+        <v>0.4817229697174627</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4866306598104315</v>
+        <v>0.4581891321377697</v>
       </c>
       <c r="L7" t="n">
-        <v>0.452172605952452</v>
+        <v>0.3410294620660286</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3306373351054986</v>
+        <v>0.3135771224997562</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3428857956039999</v>
+        <v>0.3457391360966371</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3395195653839166</v>
+        <v>0.3231840806718938</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3231840806718937</v>
+        <v>0.46135383012658</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.46135383012658</v>
+        <v>0.5124059589531199</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5257615608210163</v>
+        <v>0.7185894190665459</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7185894190665461</v>
+        <v>0.6157910152859494</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6157910152859494</v>
+        <v>0.2534871004098145</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2534871004098145</v>
+        <v>0.3728878348346331</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3728878348346331</v>
+        <v>0.189383178795796</v>
       </c>
       <c r="W7" t="n">
-        <v>0.189383178795796</v>
+        <v>0.004444444444444444</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004444444444444444</v>
+        <v>0.1484894886043476</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1484894886043476</v>
+        <v>0.3364949237289993</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3364949237289993</v>
+        <v>0.2797001563255134</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2797001563255134</v>
+        <v>0.2948148212665231</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.2948148212665231</v>
+        <v>0.5583409774962689</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5583409774962689</v>
+        <v>-0.1079316834221973</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1079316834221973</v>
+        <v>0.04603756111107495</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.04603756111107495</v>
+        <v>-0.01561413116556806</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05911784799055923</v>
+        <v>-0.1563561354841596</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.1563561354841596</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH7" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ7" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM7" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
-        <v>100</v>
+        <v>2392.305146411058</v>
       </c>
       <c r="AO7" t="n">
-        <v>2392.305146411058</v>
+        <v>0.03947587897505709</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03947587897505709</v>
-      </c>
-      <c r="AQ7" t="n">
         <v>7.780012676504056</v>
       </c>
     </row>
@@ -1462,105 +1439,102 @@
         <v>0.1504051577932513</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4491841912228889</v>
+        <v>0.009644249733570186</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01065921917711803</v>
+        <v>0.2284728763831992</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2298714811555191</v>
+        <v>0.2200244751533915</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2176883363946372</v>
+        <v>0.2677901352061005</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2865247594750786</v>
+        <v>0.2079859570018951</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2087831131748076</v>
+        <v>0.0731363832875622</v>
       </c>
       <c r="P8" t="n">
-        <v>0.07313638328756222</v>
+        <v>0.05730270571636062</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05730270571636061</v>
+        <v>0.3301743001695824</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3839032218227507</v>
+        <v>0.4390072565795425</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4390072565795425</v>
+        <v>0.5963589106248874</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5963589106248874</v>
+        <v>0.5782662869462417</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5782662869462417</v>
+        <v>0.5596873678664585</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5596873678664585</v>
+        <v>0.3635789169215826</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3635789169215826</v>
+        <v>0.04666666666666667</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04666666666666667</v>
+        <v>0.1051567297373063</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1051567297373063</v>
+        <v>0.4724143698004564</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.4724143698004564</v>
+        <v>0.03559057766721747</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03559057766721747</v>
+        <v>0.0158181667372477</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0158181667372477</v>
+        <v>-0.002467511355383492</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.002467511355383492</v>
+        <v>0.006703822784858542</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.006703822784858542</v>
+        <v>0.03483471481113833</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.03483471481113833</v>
+        <v>0.009392383368490673</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.008205093015889521</v>
+        <v>0.0244363404975303</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0244363404975303</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH8" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM8" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>100</v>
+        <v>299.2668305754655</v>
       </c>
       <c r="AO8" t="n">
-        <v>299.2668305754655</v>
+        <v>0.004938258483776251</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.004938258483776251</v>
-      </c>
-      <c r="AQ8" t="n">
         <v>5.70133558538106</v>
       </c>
     </row>
@@ -1595,105 +1569,102 @@
         <v>0.2420762754823466</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4440652557599771</v>
+        <v>0.03884265227640725</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04013598895879208</v>
+        <v>0.1981355867772255</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1968516465199397</v>
+        <v>0.1572135567635841</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1549545931184198</v>
+        <v>0.2311094842536609</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2601646090048121</v>
+        <v>0.1633256330085542</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1682395624504765</v>
+        <v>0.08663989889557584</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08663989889557584</v>
+        <v>0.07712647595589892</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07712647595589892</v>
+        <v>0.3397426172447696</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3910593835512647</v>
+        <v>0.4651316394675757</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4651316394675757</v>
+        <v>0.5473272983214916</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5473272983214916</v>
+        <v>0.5236655519962626</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5236655519962626</v>
+        <v>0.4790465135696856</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4790465135696856</v>
+        <v>0.3428080419573591</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3428080419573591</v>
+        <v>0.08444444444444445</v>
       </c>
       <c r="X9" t="n">
-        <v>0.08444444444444445</v>
+        <v>0.2339890741933288</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2339890741933288</v>
+        <v>0.3483446876036418</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3483446876036418</v>
+        <v>0.04806795681219781</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04806795681219781</v>
+        <v>0.03747679949047265</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03747679949047265</v>
+        <v>0.01307472483607221</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01307472483607221</v>
+        <v>-0.005197248302921788</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.005197248302921788</v>
+        <v>0.03897965363301479</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.03897965363301479</v>
+        <v>0.005429484591388718</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.007375394611487233</v>
+        <v>0.007542945640693687</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.007542945640693687</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH9" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ9" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM9" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN9" t="n">
-        <v>100</v>
+        <v>543.8780790436812</v>
       </c>
       <c r="AO9" t="n">
-        <v>543.8780790436812</v>
+        <v>0.008974634886241138</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.008974634886241138</v>
-      </c>
-      <c r="AQ9" t="n">
         <v>6.298725102332438</v>
       </c>
     </row>
@@ -1728,105 +1699,102 @@
         <v>0.1319140902545082</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5878639159507106</v>
+        <v>0.007861488661276053</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008228186003674072</v>
+        <v>0.3425613430432314</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3491353097578615</v>
+        <v>0.3680510479617638</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3634324005243063</v>
+        <v>0.3631711620862867</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3681961496538981</v>
+        <v>0.3322118846610039</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3259233378033231</v>
+        <v>0.03767171383652988</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0376717138365299</v>
+        <v>0.05481428045548187</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.05481428045548185</v>
+        <v>0.3360612281306767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3885109518447517</v>
+        <v>0.4668592837474414</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4668592837474414</v>
+        <v>0.6357835393459398</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6357835393459398</v>
+        <v>0.6714102933264737</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6714102933264737</v>
+        <v>0.8328870524207171</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8328870524207171</v>
+        <v>0.4996106313370194</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4996106313370194</v>
+        <v>0.07666666666666667</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07666666666666667</v>
+        <v>0.0555239060202474</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0555239060202474</v>
+        <v>0.5223568173095837</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5223568173095837</v>
+        <v>0.0170143353803188</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0170143353803188</v>
+        <v>0.01174945917028279</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01174945917028279</v>
+        <v>-0.009063105994343287</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.009063105994343287</v>
+        <v>0.006483084463370277</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.006483084463370277</v>
+        <v>0.01661043278833238</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.01661043278833238</v>
+        <v>0.002357210070652354</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001477666387859368</v>
+        <v>0.006425760323168106</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.006425760323168106</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH10" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ10" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM10" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN10" t="n">
-        <v>100</v>
+        <v>121.1803886307211</v>
       </c>
       <c r="AO10" t="n">
-        <v>121.1803886307211</v>
+        <v>0.001999620476055596</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001999620476055596</v>
-      </c>
-      <c r="AQ10" t="n">
         <v>4.797280250565018</v>
       </c>
     </row>
@@ -1861,105 +1829,102 @@
         <v>0.4711369984475785</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3496275182644208</v>
+        <v>0.05361837605909077</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05595741524671614</v>
+        <v>0.1366155674761129</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1326242266161869</v>
+        <v>0.07443593214077106</v>
       </c>
       <c r="M11" t="n">
-        <v>0.07346825434695867</v>
+        <v>0.1838220278676475</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2191238206474832</v>
+        <v>0.09712575380623777</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1055645865331218</v>
+        <v>0.1132731117203565</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1132731117203565</v>
+        <v>0.09305005881621876</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.09305005881621876</v>
+        <v>0.3332491349556314</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3853898731169649</v>
+        <v>0.4639955877369914</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4639955877369914</v>
+        <v>0.2866333806121648</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2866333806121648</v>
+        <v>0.5092885474498299</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5092885474498299</v>
+        <v>0.2809921155217411</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2809921155217411</v>
+        <v>0.09426707516363259</v>
       </c>
       <c r="W11" t="n">
-        <v>0.09426707516363259</v>
+        <v>0.04777777777777778</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04777777777777778</v>
+        <v>0.4717649738070058</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4717649738070058</v>
+        <v>0.461532024613277</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.461532024613277</v>
+        <v>0.0672661979757348</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0672661979757348</v>
+        <v>0.05006893430683006</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.05006893430683006</v>
+        <v>0.06475305805521864</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.06475305805521864</v>
+        <v>0.0004507939243981058</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0004507939243981058</v>
+        <v>0.04871246049247879</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.04871246049247879</v>
+        <v>0.02741433422664738</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03345739424989455</v>
+        <v>0.008277576217224691</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.008277576217224691</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH11" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ11" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM11" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN11" t="n">
-        <v>100</v>
+        <v>1481.020712440467</v>
       </c>
       <c r="AO11" t="n">
-        <v>1481.020712440467</v>
+        <v>0.0244386024464987</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0244386024464987</v>
-      </c>
-      <c r="AQ11" t="n">
         <v>7.300486799612587</v>
       </c>
     </row>
@@ -1994,105 +1959,102 @@
         <v>0.4427856914559749</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3605648798324952</v>
+        <v>0.09111901646559932</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0910753681870128</v>
+        <v>0.1568547508210429</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1494065809172398</v>
+        <v>0.1145631161510657</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1112822979256792</v>
+        <v>0.2109413630750346</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2313081536785767</v>
+        <v>0.1274568993159804</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1273618139278035</v>
+        <v>0.1689873106146917</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1689873106146918</v>
+        <v>0.1374727300833208</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1374727300833208</v>
+        <v>0.367273720714394</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4101244691267755</v>
+        <v>0.4184791754952872</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4184791754952872</v>
+        <v>0.3041930472299178</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3041930472299178</v>
+        <v>0.6188620153578493</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6188620153578493</v>
+        <v>0.1944145082713253</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1944145082713253</v>
+        <v>0.08054110505238374</v>
       </c>
       <c r="W12" t="n">
-        <v>0.08054110505238374</v>
+        <v>0.03888888888888889</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03888888888888889</v>
+        <v>0.4589052666076371</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4589052666076371</v>
+        <v>0.1795358278966602</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1795358278966602</v>
+        <v>0.104784313413528</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.104784313413528</v>
+        <v>0.08175030683778946</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.08175030683778946</v>
+        <v>0.167305016642337</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.167305016642337</v>
+        <v>0.01581494445656813</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.01581494445656813</v>
+        <v>0.0695130003018877</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0695130003018877</v>
+        <v>0.02760793412371342</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0512366772235345</v>
+        <v>0.03771087336959056</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.03771087336959056</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH12" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM12" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>100</v>
+        <v>1640.432240034044</v>
       </c>
       <c r="AO12" t="n">
-        <v>1640.432240034044</v>
+        <v>0.02706908216600843</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.02706908216600843</v>
-      </c>
-      <c r="AQ12" t="n">
         <v>7.402715047088515</v>
       </c>
     </row>
@@ -2127,105 +2089,102 @@
         <v>0.07012467105169649</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1434520707354031</v>
+        <v>0.01515595000127943</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01750618203003422</v>
+        <v>0.2882115283869602</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2938478120558171</v>
+        <v>0.2893918768172526</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2866225631433422</v>
+        <v>0.3206580608778492</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3335694404835768</v>
+        <v>0.271766911075668</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2703458127691244</v>
+        <v>0.05517392021183942</v>
       </c>
       <c r="P13" t="n">
-        <v>0.05517392021183942</v>
+        <v>0.058524068362829</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.05852406836282899</v>
+        <v>0.3272076023922347</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3833797056275062</v>
+        <v>0.471743763247589</v>
       </c>
       <c r="S13" t="n">
-        <v>0.471743763247589</v>
+        <v>0.2375102766452694</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2375102766452694</v>
+        <v>0.200033784666725</v>
       </c>
       <c r="U13" t="n">
-        <v>0.200033784666725</v>
+        <v>0.2552293875257215</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2552293875257215</v>
+        <v>0.1306731250147753</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1306731250147753</v>
+        <v>0.003333333333333334</v>
       </c>
       <c r="X13" t="n">
-        <v>0.003333333333333334</v>
+        <v>0.04651040251334013</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04651040251334013</v>
+        <v>0.2222187185910035</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.2222187185910035</v>
+        <v>0.03781855285768892</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.03781855285768892</v>
+        <v>0.01741642906662504</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01741642906662504</v>
+        <v>0.008434295756036764</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.008434295756036764</v>
+        <v>0.007886843660239562</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.007886843660239562</v>
+        <v>0.02042896120074602</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.02042896120074602</v>
+        <v>0.01527296738929809</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01284215664521147</v>
+        <v>0.003267199938420617</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.003267199938420617</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH13" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ13" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM13" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN13" t="n">
-        <v>100</v>
+        <v>307.3690795761586</v>
       </c>
       <c r="AO13" t="n">
-        <v>307.3690795761586</v>
+        <v>0.005071955224535667</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.005071955224535667</v>
-      </c>
-      <c r="AQ13" t="n">
         <v>5.728049239110217</v>
       </c>
     </row>
@@ -2260,105 +2219,102 @@
         <v>0.3280898687553914</v>
       </c>
       <c r="J14" t="n">
-        <v>0.405304800405938</v>
+        <v>0.0773353276572159</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08178405566220211</v>
+        <v>0.144840916178343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1424196174441631</v>
+        <v>0.1152627155268247</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1139314846983473</v>
+        <v>0.1942598219197131</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2112864108949263</v>
+        <v>0.1165897155826835</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1171238390409153</v>
+        <v>0.2082409240535934</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2082409240535935</v>
+        <v>0.1060887383607155</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1060887383607155</v>
+        <v>0.3301805674022597</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3846182594795103</v>
+        <v>0.4151204449424001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4151204449424001</v>
+        <v>0.5412760032646214</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5412760032646214</v>
+        <v>0.4474903511883088</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4474903511883088</v>
+        <v>0.571502244919594</v>
       </c>
       <c r="V14" t="n">
-        <v>0.571502244919594</v>
+        <v>0.2658892509662596</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2658892509662596</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.3079375967432389</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3079375967432389</v>
+        <v>0.5811705444808809</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.5811705444808809</v>
+        <v>0.1114817754663023</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.1114817754663023</v>
+        <v>0.06105632460223243</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.06105632460223243</v>
+        <v>0.1089129648576096</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1089129648576096</v>
+        <v>-0.03629326460902568</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.03629326460902568</v>
+        <v>0.09771537679263524</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.09771537679263524</v>
+        <v>0.04607523576456057</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0535022028684834</v>
+        <v>0.03988280453791049</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.03988280453791049</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH14" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM14" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN14" t="n">
-        <v>100</v>
+        <v>1020.135260505988</v>
       </c>
       <c r="AO14" t="n">
-        <v>1020.135260505988</v>
+        <v>0.01683344457220977</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.01683344457220977</v>
-      </c>
-      <c r="AQ14" t="n">
         <v>6.927690505825812</v>
       </c>
     </row>
@@ -2393,105 +2349,102 @@
         <v>0.297262510513997</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4530070938524989</v>
+        <v>0.04926738230900282</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05452034053675623</v>
+        <v>0.1015550045296841</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09921013655052739</v>
+        <v>0.125347178637057</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1246651895106109</v>
+        <v>0.1884198314723715</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2014387994606225</v>
+        <v>0.1016489023672338</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1016625111292161</v>
+        <v>0.2632853979479302</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2632853979479301</v>
+        <v>0.09785147264274617</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.09785147264274616</v>
+        <v>0.2988278385833515</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3580062578211431</v>
+        <v>0.3333181855367324</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3333181855367324</v>
+        <v>0.545658240093542</v>
       </c>
       <c r="T15" t="n">
-        <v>0.545658240093542</v>
+        <v>0.5643722380929105</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5643722380929105</v>
+        <v>0.5538999789618583</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5538999789618583</v>
+        <v>0.2848282766311608</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2848282766311608</v>
+        <v>0.1511111111111111</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1511111111111111</v>
+        <v>0.2748477150757934</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.2748477150757934</v>
+        <v>0.5634685486895024</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5634685486895024</v>
+        <v>0.1321127295426907</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1321127295426907</v>
+        <v>0.05380469954963863</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.05380469954963863</v>
+        <v>-0.03073157446041366</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.03073157446041366</v>
+        <v>-0.001459293719983224</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.001459293719983224</v>
+        <v>0.1295774892219866</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.1295774892219866</v>
+        <v>0.02909724697338812</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.02173459458925909</v>
+        <v>0.09278043179456574</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.09278043179456574</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH15" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM15" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>100</v>
+        <v>1062.588668527641</v>
       </c>
       <c r="AO15" t="n">
-        <v>1062.588668527641</v>
+        <v>0.01753397627472091</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.01753397627472091</v>
-      </c>
-      <c r="AQ15" t="n">
         <v>6.968463350048484</v>
       </c>
     </row>
@@ -2526,105 +2479,102 @@
         <v>0.8313509481999857</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6091324658341369</v>
+        <v>0.04684644778342291</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04931315008062453</v>
+        <v>0.009956328699082067</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.1119488757171484</v>
       </c>
       <c r="N16" t="n">
-        <v>0.126070743573698</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.2532668460912194</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2532668460912194</v>
+        <v>0.09224229137825173</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.09224229137825171</v>
+        <v>0.3413434685076035</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3944780169433278</v>
+        <v>0.3007076172156397</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3007076172156397</v>
+        <v>0.4121362856192721</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4121362856192721</v>
+        <v>0.5938664659037624</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5938664659037624</v>
+        <v>0.261418661804807</v>
       </c>
       <c r="V16" t="n">
-        <v>0.261418661804807</v>
+        <v>0.1260155018012684</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1260155018012684</v>
+        <v>0.2733333333333333</v>
       </c>
       <c r="X16" t="n">
-        <v>0.2733333333333333</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0.2059988925812638</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.2059988925812638</v>
+        <v>0.1300812255858924</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.1300812255858924</v>
+        <v>0.04911875769032343</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.04911875769032343</v>
+        <v>0.2099198866971541</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2099198866971541</v>
+        <v>0.00822743750919883</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.00822743750919883</v>
+        <v>0.1226757283933876</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.1226757283933876</v>
+        <v>0.07372561146511762</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09031390717878204</v>
+        <v>0.1138681340195404</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.1138681340195404</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH16" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM16" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>100</v>
+        <v>3131.001584605154</v>
       </c>
       <c r="AO16" t="n">
-        <v>3131.001584605154</v>
+        <v>0.05166524839442353</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.05166524839442353</v>
-      </c>
-      <c r="AQ16" t="n">
         <v>8.049108227428212</v>
       </c>
     </row>
@@ -2659,105 +2609,102 @@
         <v>0.3491877858942061</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3059859868306005</v>
+        <v>0.06711987957455187</v>
       </c>
       <c r="K17" t="n">
-        <v>0.07372145414203261</v>
+        <v>0.08617070901936748</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0836463505619668</v>
+        <v>0.1084629447824246</v>
       </c>
       <c r="M17" t="n">
-        <v>0.107890077031188</v>
+        <v>0.1787964954211494</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1779447865889229</v>
+        <v>0.08713203808469124</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0814522838012262</v>
+        <v>0.3048170334419157</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3048170334419157</v>
+        <v>0.09081558628631627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.09081558628631627</v>
+        <v>0.3147818789593368</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3751482930962308</v>
+        <v>0.3250686193452484</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3250686193452484</v>
+        <v>0.5419304452822443</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5419304452822443</v>
+        <v>0.3555124750933402</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3555124750933402</v>
+        <v>0.5798131615410689</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5798131615410689</v>
+        <v>0.2264357133169807</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2264357133169807</v>
+        <v>0.005555555555555556</v>
       </c>
       <c r="X17" t="n">
-        <v>0.005555555555555556</v>
+        <v>0.285495934702049</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.285495934702049</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>0.1640262443220279</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.1640262443220279</v>
+        <v>0.04920779753100053</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.04920779753100053</v>
+        <v>0.1795522209752033</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1795522209752033</v>
+        <v>-0.02066356838628111</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.02066356838628111</v>
+        <v>0.1431813544838578</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.1431813544838578</v>
+        <v>0.09626846991416807</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1002990502852414</v>
+        <v>0.09811503355980733</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.09811503355980733</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH17" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ17" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM17" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
-        <v>100</v>
+        <v>1400.023458553878</v>
       </c>
       <c r="AO17" t="n">
-        <v>1400.023458553878</v>
+        <v>0.02310205146489179</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.02310205146489179</v>
-      </c>
-      <c r="AQ17" t="n">
         <v>7.244244271572881</v>
       </c>
     </row>
@@ -2792,105 +2739,102 @@
         <v>0.1665901144674387</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1653847265927672</v>
+        <v>0.02114450026148435</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02488923374655185</v>
+        <v>0.228470072656473</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2323095089965548</v>
+        <v>0.2096684923385136</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2084657093051238</v>
+        <v>0.2700860544678855</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2884139050493291</v>
+        <v>0.2057990071576669</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2077382560041582</v>
+        <v>0.0806403511134199</v>
       </c>
       <c r="P18" t="n">
-        <v>0.08064035111341991</v>
+        <v>0.0623721575316686</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.06237215753166858</v>
+        <v>0.3169917029485306</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3756911816367574</v>
+        <v>0.4668010421903802</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4668010421903802</v>
+        <v>0.1889868646119849</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1889868646119849</v>
+        <v>0.266889700493161</v>
       </c>
       <c r="U18" t="n">
-        <v>0.266889700493161</v>
+        <v>0.191800144831931</v>
       </c>
       <c r="V18" t="n">
-        <v>0.191800144831931</v>
+        <v>0.1084231283997734</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1084231283997734</v>
+        <v>0.03111111111111111</v>
       </c>
       <c r="X18" t="n">
-        <v>0.03111111111111111</v>
+        <v>0.1673092215280353</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1673092215280353</v>
+        <v>0.1552780387348107</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.1552780387348107</v>
+        <v>0.05361168668225892</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.05361168668225892</v>
+        <v>0.02326147601064438</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.02326147601064438</v>
+        <v>0.04534431772020944</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.04534431772020944</v>
+        <v>-0.00322640651366978</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.00322640651366978</v>
+        <v>0.03091226955722056</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.03091226955722056</v>
+        <v>0.03686850513148932</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.03516792899412285</v>
+        <v>0.006463422365740712</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.006463422365740712</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH18" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ18" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM18" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>100</v>
+        <v>722.2370568545691</v>
       </c>
       <c r="AO18" t="n">
-        <v>722.2370568545691</v>
+        <v>0.0119177700597537</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0119177700597537</v>
-      </c>
-      <c r="AQ18" t="n">
         <v>6.582353418596734</v>
       </c>
     </row>
@@ -2925,105 +2869,102 @@
         <v>0.2916031632526555</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3089199617099119</v>
+        <v>0.09328927477646995</v>
       </c>
       <c r="K19" t="n">
-        <v>0.09890127487297895</v>
+        <v>0.1506541191950277</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1490209874277699</v>
+        <v>0.09735748868659788</v>
       </c>
       <c r="M19" t="n">
-        <v>0.09645193403612703</v>
+        <v>0.2011190712449819</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2161115274999627</v>
+        <v>0.1160752799133716</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1163392164179994</v>
+        <v>0.1911631376720676</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1911631376720676</v>
+        <v>0.1093392642984093</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1093392642984093</v>
+        <v>0.3472231518486408</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4026277660476996</v>
+        <v>0.4496174992859345</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4496174992859345</v>
+        <v>0.4563733811392492</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4563733811392492</v>
+        <v>0.293556582341794</v>
       </c>
       <c r="U19" t="n">
-        <v>0.293556582341794</v>
+        <v>0.502827396194652</v>
       </c>
       <c r="V19" t="n">
-        <v>0.502827396194652</v>
+        <v>0.2558304494763848</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2558304494763848</v>
+        <v>0.09888888888888889</v>
       </c>
       <c r="X19" t="n">
-        <v>0.09888888888888889</v>
+        <v>0.2555161742496067</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2555161742496067</v>
+        <v>0.6747414006942141</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.6747414006942141</v>
+        <v>0.1157676367117589</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1157676367117589</v>
+        <v>0.06300814516253704</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.06300814516253704</v>
+        <v>0.2575723267082795</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.2575723267082795</v>
+        <v>-0.02386557753524662</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.02386557753524662</v>
+        <v>0.08058230171796413</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.08058230171796413</v>
+        <v>0.08719130683700593</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1037990110810122</v>
+        <v>0.01757520160157355</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.01757520160157355</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH19" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ19" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM19" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>100</v>
+        <v>1312.067406343775</v>
       </c>
       <c r="AO19" t="n">
-        <v>1312.067406343775</v>
+        <v>0.02165067203807463</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.02165067203807463</v>
-      </c>
-      <c r="AQ19" t="n">
         <v>7.179359344970706</v>
       </c>
     </row>
@@ -3058,105 +2999,102 @@
         <v>0.206662313241931</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1504715527287565</v>
+        <v>0.04966376002479041</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05427734688590912</v>
+        <v>0.1039019712316544</v>
       </c>
       <c r="L20" t="n">
-        <v>0.100951623676353</v>
+        <v>0.08951476131099534</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08916081431744539</v>
+        <v>0.1678470743459353</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1715244268375169</v>
+        <v>0.08340237280356452</v>
       </c>
       <c r="O20" t="n">
-        <v>0.07896364579607439</v>
+        <v>0.2226161127125235</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2226161127125235</v>
+        <v>0.05753360691013107</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.05753360691013105</v>
+        <v>0.3446698493895909</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4023622141551334</v>
+        <v>0.3694002942288728</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3694002942288727</v>
+        <v>0.3445346470583373</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3445346470583373</v>
+        <v>0.1638209968293652</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1638209968293652</v>
+        <v>0.4393533033043008</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4393533033043008</v>
+        <v>0.1930381487221232</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1930381487221232</v>
+        <v>0.005555555555555556</v>
       </c>
       <c r="X20" t="n">
-        <v>0.005555555555555556</v>
+        <v>0.1814164537234274</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1814164537234274</v>
+        <v>0.4600497493345898</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.4600497493345898</v>
+        <v>0.1512029357320339</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1512029357320339</v>
+        <v>0.02102352051122974</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.02102352051122974</v>
+        <v>0.3109979624852583</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.3109979624852583</v>
+        <v>-0.03893829113271054</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.03893829113271054</v>
+        <v>0.08015224728816542</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.08015224728816542</v>
+        <v>0.1183926834851673</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.1334702888034321</v>
+        <v>0.06944784966177053</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.06944784966177053</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH20" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ20" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM20" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>100</v>
+        <v>1545.797579082898</v>
       </c>
       <c r="AO20" t="n">
-        <v>1545.797579082898</v>
+        <v>0.02550749775519134</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.02550749775519134</v>
-      </c>
-      <c r="AQ20" t="n">
         <v>7.343295288545848</v>
       </c>
     </row>
@@ -3191,105 +3129,102 @@
         <v>0.1925363924042419</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1656555806964768</v>
+        <v>0.1831799714307251</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1921629736522329</v>
+        <v>0.1844420786764618</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1837913236988149</v>
+        <v>0.09650445192459815</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09586792949966967</v>
+        <v>0.220460219250328</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2269495243928211</v>
+        <v>0.1358250341817905</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1323790266670651</v>
+        <v>0.2627415053689793</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2627415053689793</v>
+        <v>0.1487949700384261</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1487949700384261</v>
+        <v>0.3758176210737486</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4294769845167263</v>
+        <v>0.5224750540566209</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5224750540566209</v>
+        <v>0.4469734702683863</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4469734702683863</v>
+        <v>0.1299965672126184</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1299965672126184</v>
+        <v>0.5193459692068163</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5193459692068163</v>
+        <v>0.2042909267407435</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2042909267407435</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.1497236130405935</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1497236130405935</v>
+        <v>0.5452170227525948</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.5452170227525948</v>
+        <v>0.1779814969184534</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.1779814969184534</v>
+        <v>0.09062562348529345</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.09062562348529345</v>
+        <v>0.4977567692380653</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.4977567692380653</v>
+        <v>-0.03340640528184592</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.03340640528184592</v>
+        <v>0.09460429937586783</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.09460429937586783</v>
+        <v>0.1621654880263306</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.190344771878902</v>
+        <v>-0.02953831094798431</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.02953831094798431</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH21" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ21" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM21" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN21" t="n">
-        <v>100</v>
+        <v>2337.412973375476</v>
       </c>
       <c r="AO21" t="n">
-        <v>2337.412973375476</v>
+        <v>0.03857009286216036</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.03857009286216036</v>
-      </c>
-      <c r="AQ21" t="n">
         <v>7.756800029828256</v>
       </c>
     </row>
@@ -3324,105 +3259,102 @@
         <v>0.08812061644618377</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1869639522972435</v>
+        <v>0.02763702290638349</v>
       </c>
       <c r="K22" t="n">
-        <v>0.02986367253099145</v>
+        <v>0.1845847231173738</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1841962711555078</v>
+        <v>0.1548505506392052</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1528089838212483</v>
+        <v>0.2280050893209173</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2458362348969915</v>
+        <v>0.1564724378438356</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1572095365305465</v>
+        <v>0.1070894026124833</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1070894026124833</v>
+        <v>0.05510638671488804</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.05510638671488803</v>
+        <v>0.3495105494398055</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4041034246863612</v>
+        <v>0.4304461183499371</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4304461183499371</v>
+        <v>0.3498506104511483</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3498506104511483</v>
+        <v>0.06528494805288303</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06528494805288303</v>
+        <v>0.4995084579611674</v>
       </c>
       <c r="V22" t="n">
-        <v>0.4995084579611674</v>
+        <v>0.3524692826305258</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3524692826305258</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.03938366733634243</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.03938366733634243</v>
+        <v>0.3347923308564442</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.3347923308564442</v>
+        <v>0.08514670669107131</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.08514670669107131</v>
+        <v>0.01293524750522326</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.01293524750522326</v>
+        <v>0.1530698826726272</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.1530698826726272</v>
+        <v>0.002368504854323652</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.002368504854323652</v>
+        <v>0.0273966663517196</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.0273966663517196</v>
+        <v>0.04142420115053653</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.05167974387437069</v>
+        <v>0.0299724210685639</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.0299724210685639</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH22" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM22" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>100</v>
+        <v>606.8503125784142</v>
       </c>
       <c r="AO22" t="n">
-        <v>606.8503125784142</v>
+        <v>0.01001375160324335</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.01001375160324335</v>
-      </c>
-      <c r="AQ22" t="n">
         <v>6.408282158635725</v>
       </c>
     </row>
@@ -3457,105 +3389,102 @@
         <v>0.1861905898404718</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2719671249112984</v>
+        <v>0.1354963238602296</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1434151841436686</v>
+        <v>0.2469687660146793</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2506868199584197</v>
+        <v>0.166682210357137</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1645046561855016</v>
+        <v>0.2734670415957345</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3006519964685625</v>
+        <v>0.2009114098878049</v>
       </c>
       <c r="O23" t="n">
-        <v>0.206396794202897</v>
+        <v>0.153089494048661</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1530894940486611</v>
+        <v>0.1394130008530467</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1394130008530467</v>
+        <v>0.3478723511626063</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4040936166868785</v>
+        <v>0.5567383888033122</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5567383888033122</v>
+        <v>0.4958183964414327</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4958183964414327</v>
+        <v>0.1240911929580477</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1240911929580477</v>
+        <v>0.6397816291065365</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6397816291065365</v>
+        <v>0.3658317070168295</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3658317070168295</v>
+        <v>0.04333333333333333</v>
       </c>
       <c r="X23" t="n">
-        <v>0.04333333333333333</v>
+        <v>0.07651708503983633</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.07651708503983633</v>
+        <v>0.7715303230315101</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.7715303230315101</v>
+        <v>0.1013091417843364</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.1013091417843364</v>
+        <v>0.08332627761414804</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.08332627761414804</v>
+        <v>0.1415127288603882</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.1415127288603882</v>
+        <v>0.006391519085980836</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.006391519085980836</v>
+        <v>0.0580959704524768</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.0580959704524768</v>
+        <v>0.0390142236842343</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.04661159406495117</v>
+        <v>-0.05169477854641968</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.05169477854641968</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH23" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM23" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN23" t="n">
-        <v>100</v>
+        <v>747.1702100175625</v>
       </c>
       <c r="AO23" t="n">
-        <v>747.1702100175625</v>
+        <v>0.01232919672838144</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.01232919672838144</v>
-      </c>
-      <c r="AQ23" t="n">
         <v>6.616293017299672</v>
       </c>
     </row>
@@ -3590,105 +3519,102 @@
         <v>0.1542495576328865</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4351132529164952</v>
+        <v>0.02070725331064444</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02218714520421395</v>
+        <v>0.2185694541420376</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2194290416440928</v>
+        <v>0.2025771922070875</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2000856094758694</v>
+        <v>0.2546643186300598</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2719861365285326</v>
+        <v>0.1938605222180586</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1939160624510635</v>
+        <v>0.09519506657712286</v>
       </c>
       <c r="P24" t="n">
-        <v>0.09519506657712284</v>
+        <v>0.05795809025261758</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.05795809025261756</v>
+        <v>0.3382676893032384</v>
       </c>
       <c r="R24" t="n">
-        <v>0.391894910600414</v>
+        <v>0.4343508313004479</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4343508313004479</v>
+        <v>0.4682110827475822</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4682110827475822</v>
+        <v>0.30727898107167</v>
       </c>
       <c r="U24" t="n">
-        <v>0.30727898107167</v>
+        <v>0.6973480818275886</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6973480818275886</v>
+        <v>0.4827000323283083</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4827000323283083</v>
+        <v>0.1522222222222222</v>
       </c>
       <c r="X24" t="n">
-        <v>0.1522222222222222</v>
+        <v>0.1192519128458648</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1192519128458648</v>
+        <v>0.4331546239898784</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.4331546239898784</v>
+        <v>0.05548616833574598</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.05548616833574598</v>
+        <v>0.01867219693509392</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.01867219693509392</v>
+        <v>0.03485409347007216</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.03485409347007216</v>
+        <v>-0.009961647425431748</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.009961647425431748</v>
+        <v>0.04147811380797377</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.04147811380797377</v>
+        <v>0.01320203755371618</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.01495331228351122</v>
+        <v>0.02744742907322006</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.02744742907322006</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH24" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ24" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM24" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN24" t="n">
-        <v>100</v>
+        <v>356.1782842862052</v>
       </c>
       <c r="AO24" t="n">
-        <v>356.1782842862052</v>
+        <v>0.005877365128407318</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.005877365128407318</v>
-      </c>
-      <c r="AQ24" t="n">
         <v>5.87543140405104</v>
       </c>
     </row>
@@ -3723,105 +3649,102 @@
         <v>0.6540817343941265</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6867085353588682</v>
+        <v>0.1149203852460298</v>
       </c>
       <c r="K25" t="n">
-        <v>0.134910498684233</v>
+        <v>0.02334507508805591</v>
       </c>
       <c r="L25" t="n">
-        <v>0.03002413352658418</v>
+        <v>0.1452732933084691</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1459358134944441</v>
+        <v>0.2580452513372229</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2757374935465507</v>
+        <v>0.1075825000086291</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1171985789332565</v>
+        <v>0.4198819832081659</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4198819832081658</v>
+        <v>0.2654763888308522</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2654763888308522</v>
+        <v>0.1630981845965951</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2487396195443453</v>
+        <v>0.300018709455746</v>
       </c>
       <c r="S25" t="n">
-        <v>0.300018709455746</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0.3213012329167896</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3213012329167896</v>
+        <v>0.1895658754548945</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1895658754548945</v>
+        <v>0.1177777777777778</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1177777777777778</v>
+        <v>0.6776273892403746</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.6776273892403746</v>
+        <v>0.3593130591888976</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.3593130591888976</v>
+        <v>0.2184486631476414</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.2184486631476414</v>
+        <v>0.1640966306274615</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.1640966306274615</v>
+        <v>-0.2786529764483485</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.2786529764483485</v>
+        <v>0.2399691716102233</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.2399691716102233</v>
+        <v>0.2041169216982499</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.2041169216982499</v>
+        <v>0.07509556838980538</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.03605092240308415</v>
+        <v>0.1143136178748989</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.1143136178748989</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH25" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ25" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM25" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN25" t="n">
-        <v>100</v>
+        <v>2725.179712298798</v>
       </c>
       <c r="AO25" t="n">
-        <v>2725.179712298798</v>
+        <v>0.04496870504558264</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.04496870504558264</v>
-      </c>
-      <c r="AQ25" t="n">
         <v>7.910289654390223</v>
       </c>
     </row>
@@ -3856,105 +3779,102 @@
         <v>0.134205419093004</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3417292365919214</v>
+        <v>0.009179398987246694</v>
       </c>
       <c r="K26" t="n">
-        <v>0.01005428229243791</v>
+        <v>0.3912826609771002</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4008295848939624</v>
+        <v>0.4304610205037775</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4251042594579308</v>
+        <v>0.397696224589795</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3964555798305114</v>
+        <v>0.3825108069075855</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3731619301109829</v>
+        <v>0.02866595498280556</v>
       </c>
       <c r="P26" t="n">
-        <v>0.02866595498280557</v>
+        <v>0.0516485372290349</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.05164853722903488</v>
+        <v>0.3395887014542781</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3930494911454814</v>
+        <v>0.4786186251265056</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4786186251265056</v>
+        <v>0.5544949009691386</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5544949009691386</v>
+        <v>0.1777130253582353</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1777130253582353</v>
+        <v>0.7257264120230366</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7257264120230366</v>
+        <v>0.3381319731146193</v>
       </c>
       <c r="W26" t="n">
-        <v>0.3381319731146193</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.005609787249957732</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.005609787249957732</v>
+        <v>0.6051678639756862</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.6051678639756862</v>
+        <v>0.01558457870625312</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.01558457870625312</v>
+        <v>0.008282283636133477</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.008282283636133477</v>
+        <v>-0.008336948411674022</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.008336948411674022</v>
+        <v>-0.01005463568364197</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.01005463568364197</v>
+        <v>0.011065969760812</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.011065969760812</v>
+        <v>-0.0004886849921523742</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.002424347776411811</v>
+        <v>-0.001178445985715371</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.001178445985715371</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH26" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM26" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN26" t="n">
-        <v>100</v>
+        <v>85.20628897198911</v>
       </c>
       <c r="AO26" t="n">
-        <v>85.20628897198911</v>
+        <v>0.001406005064369842</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.001406005064369842</v>
-      </c>
-      <c r="AQ26" t="n">
         <v>4.445075245336358</v>
       </c>
     </row>
@@ -3989,105 +3909,102 @@
         <v>0.1146588415869427</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4232224527522012</v>
+        <v>0.01314555874387556</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01325832785021473</v>
+        <v>0.2221592524772774</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2220682041745093</v>
+        <v>0.2291786890126891</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2261874944299692</v>
+        <v>0.2850708270688582</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2942444895845859</v>
+        <v>0.2154482818057085</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2120158655061994</v>
+        <v>0.114076639781028</v>
       </c>
       <c r="P27" t="n">
-        <v>0.114076639781028</v>
+        <v>0.06536592730052967</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.06536592730052965</v>
+        <v>0.3319783591165993</v>
       </c>
       <c r="R27" t="n">
-        <v>0.383303923391792</v>
+        <v>0.3964762099504138</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3964762099504138</v>
+        <v>0.2674762256015769</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2674762256015769</v>
+        <v>0.7816893713802218</v>
       </c>
       <c r="U27" t="n">
-        <v>0.7816893713802218</v>
+        <v>0.2909914075437558</v>
       </c>
       <c r="V27" t="n">
-        <v>0.2909914075437558</v>
+        <v>0.1343738937790726</v>
       </c>
       <c r="W27" t="n">
-        <v>0.1343738937790726</v>
+        <v>0.23</v>
       </c>
       <c r="X27" t="n">
-        <v>0.23</v>
+        <v>0.1091840649125298</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1091840649125298</v>
+        <v>0.1802351163587163</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.1802351163587163</v>
+        <v>0.05321687590863682</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.05321687590863682</v>
+        <v>0.02318714271178382</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.02318714271178382</v>
+        <v>0.01467786475616529</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.01467786475616529</v>
+        <v>0.03513641079228535</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.03513641079228535</v>
+        <v>0.05678136556034294</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.05678136556034294</v>
+        <v>0.01283595410608849</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0153237432954916</v>
+        <v>0.0519391438157868</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.0519391438157868</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH27" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM27" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN27" t="n">
-        <v>100</v>
+        <v>511.0668191968198</v>
       </c>
       <c r="AO27" t="n">
-        <v>511.0668191968198</v>
+        <v>0.00843321009155013</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.00843321009155013</v>
-      </c>
-      <c r="AQ27" t="n">
         <v>6.236500343292759</v>
       </c>
     </row>
@@ -4122,105 +4039,102 @@
         <v>0.2501910984880433</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4297995695722087</v>
+        <v>0.163385710800698</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2026186597265137</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02431435161912338</v>
+        <v>0.2345125061425517</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2317362609495839</v>
+        <v>0.2059255299268536</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1464587227040555</v>
+        <v>0.1049256587343057</v>
       </c>
       <c r="O28" t="n">
-        <v>0.08402916038485037</v>
+        <v>0.928208970809724</v>
       </c>
       <c r="P28" t="n">
-        <v>0.928208970809724</v>
+        <v>0.08399625594578963</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.08399625594578963</v>
+        <v>0.2508337068923183</v>
       </c>
       <c r="R28" t="n">
-        <v>0.374909707982323</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>0.707339878932209</v>
       </c>
       <c r="T28" t="n">
-        <v>0.707339878932209</v>
+        <v>0.114481225005615</v>
       </c>
       <c r="U28" t="n">
-        <v>0.114481225005615</v>
+        <v>0.7985829819347966</v>
       </c>
       <c r="V28" t="n">
-        <v>0.7985829819347966</v>
+        <v>0.4172198620694987</v>
       </c>
       <c r="W28" t="n">
-        <v>0.4172198620694987</v>
+        <v>0.4611111111111111</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4611111111111111</v>
+        <v>0.1986639788346991</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1986639788346991</v>
+        <v>0.7063143261273148</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.7063143261273148</v>
+        <v>0.5569575392473969</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.5569575392473969</v>
+        <v>0.0434127108328527</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.0434127108328527</v>
+        <v>-0.08899114860813431</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.08899114860813431</v>
+        <v>-0.01016840244267849</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.01016840244267849</v>
+        <v>0.4071121483645818</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.4071121483645818</v>
+        <v>0.05495733989913592</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.01435778518507961</v>
+        <v>0.3083214359732978</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.3083214359732978</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH28" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ28" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM28" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN28" t="n">
-        <v>100</v>
+        <v>4825.169031095344</v>
       </c>
       <c r="AO28" t="n">
-        <v>4825.169031095344</v>
+        <v>0.07962102534932408</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.07962102534932408</v>
-      </c>
-      <c r="AQ28" t="n">
         <v>8.481601045510834</v>
       </c>
     </row>
@@ -4255,105 +4169,102 @@
         <v>0.1867572726577177</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2928506632334102</v>
+        <v>0.2756298969779413</v>
       </c>
       <c r="K29" t="n">
-        <v>0.2891242974917798</v>
+        <v>0.3455016300708108</v>
       </c>
       <c r="L29" t="n">
-        <v>0.3534367245500948</v>
+        <v>0.3543035341764009</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3491812515839846</v>
+        <v>0.4073083893876299</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4148257865295828</v>
+        <v>0.3469832691294576</v>
       </c>
       <c r="O29" t="n">
-        <v>0.3434657180252323</v>
+        <v>0.3702950127969951</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3702950127969951</v>
+        <v>0.298246224693777</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.298246224693777</v>
+        <v>0.3186618680382246</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3728863442345142</v>
+        <v>0.5411617179831604</v>
       </c>
       <c r="S29" t="n">
-        <v>0.5411617179831604</v>
+        <v>0.3002375797840424</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3002375797840424</v>
+        <v>0.3104388518802081</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3104388518802081</v>
+        <v>0.4634040390000416</v>
       </c>
       <c r="V29" t="n">
-        <v>0.4634040390000416</v>
+        <v>0.2837995154529202</v>
       </c>
       <c r="W29" t="n">
-        <v>0.2837995154529202</v>
+        <v>0.12</v>
       </c>
       <c r="X29" t="n">
-        <v>0.12</v>
+        <v>0.180710374200749</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.180710374200749</v>
+        <v>0.2652702205636326</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.2652702205636326</v>
+        <v>0.237938599802106</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.237938599802106</v>
+        <v>0.187536429983737</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.187536429983737</v>
+        <v>-0.001426704022974105</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.001426704022974105</v>
+        <v>0.1019047366669057</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.1019047366669057</v>
+        <v>0.1438557735725477</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.1438557735725477</v>
+        <v>0.02003851906211092</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.01899113972190745</v>
+        <v>-0.04162208699816006</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.04162208699816006</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH29" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM29" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN29" t="n">
-        <v>100</v>
+        <v>967.4980653878789</v>
       </c>
       <c r="AO29" t="n">
-        <v>967.4980653878789</v>
+        <v>0.01596486827575102</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.01596486827575102</v>
-      </c>
-      <c r="AQ29" t="n">
         <v>6.874713425302846</v>
       </c>
     </row>
@@ -4388,105 +4299,102 @@
         <v>0.4895788080958718</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8836343004979609</v>
+        <v>0.6971193486764868</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7196151689447498</v>
+        <v>0.6673676674308086</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6807152591960837</v>
+        <v>0.7765041096680819</v>
       </c>
       <c r="M30" t="n">
-        <v>0.7650920890195674</v>
+        <v>0.6099818728634007</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5589669374557038</v>
+        <v>0.6719768058851631</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6348135877210337</v>
+        <v>0.8854391916976868</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8854391916976868</v>
+        <v>0.645693174987956</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.6456931749879558</v>
+        <v>0.4222461254252959</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4529104161588298</v>
+        <v>0.5713146727529083</v>
       </c>
       <c r="S30" t="n">
-        <v>0.5713146727529083</v>
+        <v>0.3803713583914172</v>
       </c>
       <c r="T30" t="n">
-        <v>0.3803713583914172</v>
+        <v>0.2852557486150366</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2852557486150366</v>
+        <v>0.5849648871009304</v>
       </c>
       <c r="V30" t="n">
-        <v>0.5849648871009304</v>
+        <v>0.6402436056857285</v>
       </c>
       <c r="W30" t="n">
-        <v>0.6402436056857285</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0.4987799328271997</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.4987799328271997</v>
+        <v>0.3481247024645606</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3481247024645606</v>
+        <v>0.5633163615598757</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.5633163615598757</v>
+        <v>0.4131729629255305</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.4131729629255305</v>
+        <v>0.1243168744267037</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.1243168744267037</v>
+        <v>-0.02405050104991732</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.02405050104991732</v>
+        <v>0.3486790936918118</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.3486790936918118</v>
+        <v>-0.03591241489824408</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.009391153091301367</v>
+        <v>-0.06112056752529327</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.06112056752529327</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH30" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM30" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN30" t="n">
-        <v>100</v>
+        <v>2705.688079708003</v>
       </c>
       <c r="AO30" t="n">
-        <v>2705.688079708003</v>
+        <v>0.04464706993547354</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.04464706993547354</v>
-      </c>
-      <c r="AQ30" t="n">
         <v>7.903111532207864</v>
       </c>
     </row>
@@ -4521,105 +4429,102 @@
         <v>0.3886007566178959</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4259656805334142</v>
+        <v>0.6951243584122271</v>
       </c>
       <c r="K31" t="n">
-        <v>0.715492706181349</v>
+        <v>0.6877786171594643</v>
       </c>
       <c r="L31" t="n">
-        <v>0.6999165700575044</v>
+        <v>0.8158635430815903</v>
       </c>
       <c r="M31" t="n">
-        <v>0.803964363676331</v>
+        <v>0.6110545434675476</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5721947088264434</v>
+        <v>0.6916081938496924</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6581707138342092</v>
+        <v>0.8252152470298494</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8252152470298494</v>
+        <v>0.6748117838299721</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.674811783829972</v>
+        <v>0.4103534068821569</v>
       </c>
       <c r="R31" t="n">
-        <v>0.4364180968341134</v>
+        <v>0.6095969143465005</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6095969143465007</v>
+        <v>0.2742995354477744</v>
       </c>
       <c r="T31" t="n">
-        <v>0.2742995354477744</v>
+        <v>0.2692196026481981</v>
       </c>
       <c r="U31" t="n">
-        <v>0.2692196026481981</v>
+        <v>0.4163608954190312</v>
       </c>
       <c r="V31" t="n">
-        <v>0.4163608954190312</v>
+        <v>0.3539609921323707</v>
       </c>
       <c r="W31" t="n">
-        <v>0.3539609921323707</v>
+        <v>0.3011111111111112</v>
       </c>
       <c r="X31" t="n">
-        <v>0.3011111111111112</v>
+        <v>0.3970025424188013</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.3970025424188013</v>
+        <v>0.2508430537879217</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.2508430537879217</v>
+        <v>0.5836784321510459</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.5836784321510459</v>
+        <v>0.4321582390696374</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.4321582390696374</v>
+        <v>0.03398830244432301</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.03398830244432301</v>
+        <v>-0.03906955914226836</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.03906955914226836</v>
+        <v>0.2976064848754095</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.2976064848754095</v>
+        <v>-0.04861356162921902</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.02666917473073975</v>
+        <v>-0.08587587087608028</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.08587587087608028</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH31" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ31" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM31" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN31" t="n">
-        <v>100</v>
+        <v>2248.057105713534</v>
       </c>
       <c r="AO31" t="n">
-        <v>2248.057105713534</v>
+        <v>0.03709561481623639</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.03709561481623639</v>
-      </c>
-      <c r="AQ31" t="n">
         <v>7.717821613588413</v>
       </c>
     </row>
@@ -4654,105 +4559,102 @@
         <v>0.4835129610436654</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3897920424516772</v>
+        <v>0.6996025165213099</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7293522785647918</v>
+        <v>0.6664622042958805</v>
       </c>
       <c r="L32" t="n">
-        <v>0.687641460034852</v>
+        <v>0.8655470417667186</v>
       </c>
       <c r="M32" t="n">
-        <v>0.8641443812205183</v>
+        <v>0.839787259364468</v>
       </c>
       <c r="N32" t="n">
-        <v>0.7663850233195585</v>
+        <v>0.791338535895839</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7558661627706696</v>
+        <v>0.9213387244852902</v>
       </c>
       <c r="P32" t="n">
-        <v>0.9213387244852901</v>
+        <v>0.7540946530344521</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.7540946530344521</v>
+        <v>0.3177373314978831</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3645345155688163</v>
+        <v>0.5373922361934172</v>
       </c>
       <c r="S32" t="n">
-        <v>0.5373922361934172</v>
+        <v>0.3323512204536653</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3323512204536653</v>
+        <v>0.3476450221135798</v>
       </c>
       <c r="U32" t="n">
-        <v>0.3476450221135798</v>
+        <v>0.3903540389538765</v>
       </c>
       <c r="V32" t="n">
-        <v>0.3903540389538765</v>
+        <v>0.2425221700103515</v>
       </c>
       <c r="W32" t="n">
-        <v>0.2425221700103515</v>
+        <v>0.1744444444444445</v>
       </c>
       <c r="X32" t="n">
-        <v>0.1744444444444445</v>
+        <v>0.4935297872824017</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.4935297872824017</v>
+        <v>0.3288043830458387</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3288043830458387</v>
+        <v>0.613478019741355</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.613478019741355</v>
+        <v>0.4802893031891615</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.4802893031891615</v>
+        <v>0.122181307366316</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.122181307366316</v>
+        <v>0.4013996139101101</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.4013996139101101</v>
+        <v>0.3573004884550736</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.3573004884550736</v>
+        <v>0.06546110081904351</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.08345644075355653</v>
+        <v>-0.03918454255729387</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.03918454255729387</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH32" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ32" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM32" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN32" t="n">
-        <v>100</v>
+        <v>2647.41486416641</v>
       </c>
       <c r="AO32" t="n">
-        <v>2647.41486416641</v>
+        <v>0.04368549260172145</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.04368549260172145</v>
-      </c>
-      <c r="AQ32" t="n">
         <v>7.881338919892</v>
       </c>
     </row>
@@ -4787,105 +4689,102 @@
         <v>0.1217618772511367</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3581802235640802</v>
+        <v>0.04110728333684788</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03355673734211011</v>
+        <v>0.2672659967173641</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2596311384999733</v>
+        <v>0.2474771720541364</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2381011964629558</v>
+        <v>0.269935258105963</v>
       </c>
       <c r="N33" t="n">
-        <v>0.286197189468804</v>
+        <v>0.231100433518498</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2243995332408553</v>
+        <v>0.03988066053751324</v>
       </c>
       <c r="P33" t="n">
-        <v>0.03988066053751323</v>
+        <v>0.07368440263542829</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.07368440263542828</v>
+        <v>0.413735644260426</v>
       </c>
       <c r="R33" t="n">
-        <v>0.444832263005584</v>
+        <v>0.4466931212250173</v>
       </c>
       <c r="S33" t="n">
-        <v>0.4466931212250173</v>
+        <v>0.4816258590362896</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4816258590362896</v>
+        <v>0.2614163894289926</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2614163894289926</v>
+        <v>0.669226687455048</v>
       </c>
       <c r="V33" t="n">
-        <v>0.669226687455048</v>
+        <v>0.4842138988928907</v>
       </c>
       <c r="W33" t="n">
-        <v>0.4842138988928907</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.03539193046810566</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.03539193046810566</v>
+        <v>0.5086657546988665</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.5086657546988665</v>
+        <v>0.04173470919100534</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.04173470919100534</v>
+        <v>0.0349267806176761</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.0349267806176761</v>
+        <v>0.1742404205450563</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.1742404205450563</v>
+        <v>-0.01286856839729804</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.01286856839729804</v>
+        <v>-0.001663398719301727</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.001663398719301727</v>
+        <v>-0.01511910054588435</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.0172289243817706</v>
+        <v>0.01946625768911758</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.01946625768911758</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH33" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ33" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM33" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN33" t="n">
-        <v>100</v>
+        <v>272.9149685974317</v>
       </c>
       <c r="AO33" t="n">
-        <v>272.9149685974317</v>
+        <v>0.004503421433087765</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.004503421433087765</v>
-      </c>
-      <c r="AQ33" t="n">
         <v>5.609160276328921</v>
       </c>
     </row>
@@ -4920,105 +4819,102 @@
         <v>0.188337385488053</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5496551430409062</v>
+        <v>0.1160375548816566</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1195603553884284</v>
+        <v>0.2191461141217687</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2175647468418478</v>
+        <v>0.1201133039428817</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1167834896933555</v>
+        <v>0.2165470165722407</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2574237222250983</v>
+        <v>0.1538593537428591</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1628438718462809</v>
+        <v>0.1059193357725961</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1059193357725961</v>
+        <v>0.1168505452289862</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1168505452289861</v>
+        <v>0.3782298431890248</v>
       </c>
       <c r="R34" t="n">
-        <v>0.4265441933184567</v>
+        <v>0.5501163381664407</v>
       </c>
       <c r="S34" t="n">
-        <v>0.5501163381664407</v>
+        <v>0.6607178592061448</v>
       </c>
       <c r="T34" t="n">
-        <v>0.6607178592061448</v>
+        <v>0.1416222732385312</v>
       </c>
       <c r="U34" t="n">
-        <v>0.1416222732385312</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0.7562829250816511</v>
       </c>
       <c r="W34" t="n">
-        <v>0.7562829250816511</v>
+        <v>0.2544444444444444</v>
       </c>
       <c r="X34" t="n">
-        <v>0.2544444444444444</v>
+        <v>0.1036851671049531</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1036851671049531</v>
+        <v>0.7079358905313921</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.7079358905313921</v>
+        <v>0.07051133644093927</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.07051133644093927</v>
+        <v>0.06851761169620196</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.06851761169620196</v>
+        <v>0.09040773603716139</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.09040773603716139</v>
+        <v>-0.02954504708758408</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.02954504708758408</v>
+        <v>0.04029438732864574</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.04029438732864574</v>
+        <v>-0.006626595393466397</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.003086607345899264</v>
+        <v>-0.04741261361834859</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.04741261361834859</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH34" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ34" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM34" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN34" t="n">
-        <v>100</v>
+        <v>699.4028820849159</v>
       </c>
       <c r="AO34" t="n">
-        <v>699.4028820849159</v>
+        <v>0.01154097902995785</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.01154097902995785</v>
-      </c>
-      <c r="AQ34" t="n">
         <v>6.550226945417061</v>
       </c>
     </row>
@@ -5053,105 +4949,102 @@
         <v>0.4743256620658648</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6410097574826965</v>
+        <v>0.1522897593247697</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1526662585294829</v>
+        <v>0.2178040069082643</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2108879095649088</v>
+        <v>0.2364646993330674</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2313839129302518</v>
+        <v>0.272973461302967</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2805266485734487</v>
+        <v>0.2111774120253047</v>
       </c>
       <c r="O35" t="n">
-        <v>0.2038658755759715</v>
+        <v>0.2957823151877944</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2957823151877945</v>
+        <v>0.2059151755520117</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2059151755520117</v>
+        <v>0.3516006698397937</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3890295449014136</v>
+        <v>0.3835118582396892</v>
       </c>
       <c r="S35" t="n">
-        <v>0.3835118582396892</v>
+        <v>0.4422750990682222</v>
       </c>
       <c r="T35" t="n">
-        <v>0.4422750990682222</v>
+        <v>0.6210197990673766</v>
       </c>
       <c r="U35" t="n">
-        <v>0.6210197990673766</v>
+        <v>0.4786171743695299</v>
       </c>
       <c r="V35" t="n">
-        <v>0.4786171743695299</v>
+        <v>0.3915813773027342</v>
       </c>
       <c r="W35" t="n">
-        <v>0.3915813773027342</v>
+        <v>0.2844444444444444</v>
       </c>
       <c r="X35" t="n">
-        <v>0.2844444444444444</v>
+        <v>0.485375621216764</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.485375621216764</v>
+        <v>0.3022751736379541</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3022751736379541</v>
+        <v>0.1649437645274995</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.1649437645274995</v>
+        <v>0.1278711107713652</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.1278711107713652</v>
+        <v>-0.001256745857939791</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.001256745857939791</v>
+        <v>0.02146215462480688</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.02146215462480688</v>
+        <v>0.1348350346406568</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.1348350346406568</v>
+        <v>-0.00883706043597874</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.003888987920131606</v>
+        <v>0.06032257294599219</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.06032257294599219</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH35" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ35" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM35" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN35" t="n">
-        <v>100</v>
+        <v>991.3739722984393</v>
       </c>
       <c r="AO35" t="n">
-        <v>991.3739722984393</v>
+        <v>0.01635884912432085</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.01635884912432085</v>
-      </c>
-      <c r="AQ35" t="n">
         <v>6.899091831760344</v>
       </c>
     </row>
@@ -5186,105 +5079,102 @@
         <v>0.1241121248059722</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5913516184131866</v>
+        <v>0.01540004257939981</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01635622719245745</v>
+        <v>0.3004656854004149</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3051754999736183</v>
+        <v>0.3025096928182841</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2988666280480984</v>
+        <v>0.3127066088240685</v>
       </c>
       <c r="N36" t="n">
-        <v>0.3280170337980887</v>
+        <v>0.2769165905340489</v>
       </c>
       <c r="O36" t="n">
-        <v>0.2752292967426786</v>
+        <v>0.04176101422446856</v>
       </c>
       <c r="P36" t="n">
-        <v>0.04176101422446857</v>
+        <v>0.05637845320069208</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.05637845320069207</v>
+        <v>0.3360890715055607</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3890856612870125</v>
+        <v>0.4789978080234821</v>
       </c>
       <c r="S36" t="n">
-        <v>0.4789978080234821</v>
+        <v>0.6425040188948004</v>
       </c>
       <c r="T36" t="n">
-        <v>0.6425040188948004</v>
+        <v>0.4921469006042185</v>
       </c>
       <c r="U36" t="n">
-        <v>0.4921469006042185</v>
+        <v>0.8160136609106782</v>
       </c>
       <c r="V36" t="n">
-        <v>0.8160136609106782</v>
+        <v>0.6696014586385939</v>
       </c>
       <c r="W36" t="n">
-        <v>0.6696014586385939</v>
+        <v>0.1088888888888889</v>
       </c>
       <c r="X36" t="n">
-        <v>0.1088888888888889</v>
+        <v>0.03611857344260294</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.03611857344260294</v>
+        <v>0.519318200771499</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.519318200771499</v>
+        <v>0.02237365816253831</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.02237365816253831</v>
+        <v>0.01778649189288714</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.01778649189288714</v>
+        <v>-0.01451914268705567</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.01451914268705567</v>
+        <v>-0.0205896804928334</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.0205896804928334</v>
+        <v>0.01789608059356288</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.01789608059356288</v>
+        <v>0.0008139401906950168</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.001049622744756771</v>
+        <v>-0.001423645515558292</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.001423645515558292</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH36" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ36" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM36" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN36" t="n">
-        <v>100</v>
+        <v>172.6917150198915</v>
       </c>
       <c r="AO36" t="n">
-        <v>172.6917150198915</v>
+        <v>0.002849618600013214</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.002849618600013214</v>
-      </c>
-      <c r="AQ36" t="n">
         <v>5.151508010752844</v>
       </c>
     </row>
@@ -5319,105 +5209,102 @@
         <v>0.1954106614132574</v>
       </c>
       <c r="J37" t="n">
-        <v>0.2917673492090704</v>
+        <v>0.6703802749647579</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6993422090914743</v>
+        <v>0.7017334206753636</v>
       </c>
       <c r="L37" t="n">
-        <v>0.725285409898355</v>
+        <v>0.6023093159677022</v>
       </c>
       <c r="M37" t="n">
-        <v>0.5918222368050262</v>
+        <v>0.5172059983039065</v>
       </c>
       <c r="N37" t="n">
-        <v>0.5615360712285035</v>
+        <v>0.5944789437147667</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6004789470241849</v>
+        <v>0.5173950106565695</v>
       </c>
       <c r="P37" t="n">
-        <v>0.5173950106565693</v>
+        <v>0.5663800905113069</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5663800905113069</v>
+        <v>0.419255637855968</v>
       </c>
       <c r="R37" t="n">
-        <v>0.4673162462236683</v>
+        <v>0.958455869061112</v>
       </c>
       <c r="S37" t="n">
-        <v>0.9584558690611122</v>
+        <v>0.4083991521820728</v>
       </c>
       <c r="T37" t="n">
-        <v>0.4083991521820728</v>
+        <v>0.09340463776406144</v>
       </c>
       <c r="U37" t="n">
-        <v>0.09340463776406144</v>
+        <v>0.5888660779323599</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5888660779323599</v>
+        <v>0.4931775464987245</v>
       </c>
       <c r="W37" t="n">
-        <v>0.4931775464987245</v>
+        <v>0.09</v>
       </c>
       <c r="X37" t="n">
-        <v>0.09</v>
+        <v>0.1838901954276356</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1838901954276356</v>
+        <v>0.3315667799793048</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.3315667799793048</v>
+        <v>0.3601993919652881</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.3601993919652881</v>
+        <v>0.3623750428408798</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.3623750428408798</v>
+        <v>-0.1506091381776</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.1506091381776</v>
+        <v>-0.0820473995538875</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.0820473995538875</v>
+        <v>0.1772034951422113</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.1772034951422113</v>
+        <v>-0.09635134862155696</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.1147783108674245</v>
+        <v>-0.3114663507199822</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.3114663507199822</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH37" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ37" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM37" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN37" t="n">
-        <v>100</v>
+        <v>1722.207760018489</v>
       </c>
       <c r="AO37" t="n">
-        <v>1722.207760018489</v>
+        <v>0.02841847546346096</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.02841847546346096</v>
-      </c>
-      <c r="AQ37" t="n">
         <v>7.451362328127241</v>
       </c>
     </row>
@@ -5452,105 +5339,102 @@
         <v>0.05050543057151457</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4348719339775127</v>
+        <v>0.00940729705019732</v>
       </c>
       <c r="K38" t="n">
-        <v>0.008808421087818845</v>
+        <v>0.4257551734075429</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4354184408183513</v>
+        <v>0.4783528588043716</v>
       </c>
       <c r="M38" t="n">
-        <v>0.4714510628095996</v>
+        <v>0.4306501933561255</v>
       </c>
       <c r="N38" t="n">
-        <v>0.4237281224000538</v>
+        <v>0.4226695037265896</v>
       </c>
       <c r="O38" t="n">
-        <v>0.4098735514361212</v>
+        <v>0.02092657746608599</v>
       </c>
       <c r="P38" t="n">
-        <v>0.02092657746608599</v>
+        <v>0.0528735776004041</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.05287357760040409</v>
+        <v>0.3484680089737989</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3985748493214707</v>
+        <v>0.4767923664523357</v>
       </c>
       <c r="S38" t="n">
-        <v>0.4767923664523357</v>
+        <v>0.2666195499469929</v>
       </c>
       <c r="T38" t="n">
-        <v>0.2666195499469929</v>
+        <v>0.4189867975066522</v>
       </c>
       <c r="U38" t="n">
-        <v>0.4189867975066522</v>
+        <v>0.4214217022535818</v>
       </c>
       <c r="V38" t="n">
-        <v>0.4214217022535818</v>
+        <v>0.4783625554737082</v>
       </c>
       <c r="W38" t="n">
-        <v>0.4783625554737082</v>
+        <v>0.07777777777777778</v>
       </c>
       <c r="X38" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.03806899350843664</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.03806899350843664</v>
+        <v>0.1412182275199218</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.1412182275199218</v>
+        <v>0.01196483225579974</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.01196483225579974</v>
+        <v>0.008988259953933339</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.008988259953933339</v>
+        <v>-0.003213598788319244</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.003213598788319244</v>
+        <v>-5.671936614240556e-05</v>
       </c>
       <c r="AD38" t="n">
-        <v>-5.671936614240556e-05</v>
+        <v>0.00673143804365822</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.00673143804365822</v>
+        <v>-0.006697422135333779</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.005615419792633975</v>
+        <v>2.508566424808123e-06</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.508566424808123e-06</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH38" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ38" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM38" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN38" t="n">
-        <v>100</v>
+        <v>114.9648966121948</v>
       </c>
       <c r="AO38" t="n">
-        <v>114.9648966121948</v>
+        <v>0.001897057468547181</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.001897057468547181</v>
-      </c>
-      <c r="AQ38" t="n">
         <v>4.744626834915468</v>
       </c>
     </row>
@@ -5585,105 +5469,102 @@
         <v>0.06005484941039925</v>
       </c>
       <c r="J39" t="n">
-        <v>0.5551134080819151</v>
+        <v>0.01179207338000899</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01118078121976139</v>
+        <v>0.3584420048627939</v>
       </c>
       <c r="L39" t="n">
-        <v>0.3645501609885945</v>
+        <v>0.3867371187498831</v>
       </c>
       <c r="M39" t="n">
-        <v>0.3811997661166255</v>
+        <v>0.374080490404737</v>
       </c>
       <c r="N39" t="n">
-        <v>0.3786239499346251</v>
+        <v>0.3479695500500021</v>
       </c>
       <c r="O39" t="n">
-        <v>0.3406980452903323</v>
+        <v>0.03217817112111276</v>
       </c>
       <c r="P39" t="n">
-        <v>0.03217817112111276</v>
+        <v>0.05794937517519076</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.05794937517519075</v>
+        <v>0.343963509039895</v>
       </c>
       <c r="R39" t="n">
-        <v>0.393793905300387</v>
+        <v>0.4706066749382973</v>
       </c>
       <c r="S39" t="n">
-        <v>0.4706066749382973</v>
+        <v>0.3559269043022127</v>
       </c>
       <c r="T39" t="n">
-        <v>0.3559269043022127</v>
+        <v>0.513866769884049</v>
       </c>
       <c r="U39" t="n">
-        <v>0.513866769884049</v>
+        <v>0.3502120983821628</v>
       </c>
       <c r="V39" t="n">
-        <v>0.3502120983821628</v>
+        <v>0.5744591156258356</v>
       </c>
       <c r="W39" t="n">
-        <v>0.5744591156258356</v>
+        <v>0.1888888888888889</v>
       </c>
       <c r="X39" t="n">
-        <v>0.1888888888888889</v>
+        <v>0.05396933060225294</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.05396933060225294</v>
+        <v>0.1203137433683319</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.1203137433683319</v>
+        <v>0.02288516245137856</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.02288516245137856</v>
+        <v>0.01725433835034526</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.01725433835034526</v>
+        <v>-0.01929819442985124</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.01929819442985124</v>
+        <v>0.002541055220820242</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.002541055220820242</v>
+        <v>0.01102129112574966</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.01102129112574966</v>
+        <v>-0.007198995210650608</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.007065907229692389</v>
+        <v>0.00400250082105913</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.00400250082105913</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH39" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ39" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM39" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN39" t="n">
-        <v>100</v>
+        <v>138.104489924256</v>
       </c>
       <c r="AO39" t="n">
-        <v>138.104489924256</v>
+        <v>0.002278888267385421</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.002278888267385421</v>
-      </c>
-      <c r="AQ39" t="n">
         <v>4.928010572010243</v>
       </c>
     </row>
@@ -5718,105 +5599,102 @@
         <v>0.08861670793544825</v>
       </c>
       <c r="J40" t="n">
-        <v>0.3534001476245962</v>
+        <v>0.05130994594934542</v>
       </c>
       <c r="K40" t="n">
-        <v>0.05403752262191767</v>
+        <v>0.286029281447945</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2901793879337969</v>
+        <v>0.2575797390289686</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2545223997867116</v>
+        <v>0.3095541295350807</v>
       </c>
       <c r="N40" t="n">
-        <v>0.3328518141872582</v>
+        <v>0.2569240646333819</v>
       </c>
       <c r="O40" t="n">
-        <v>0.2595214032905653</v>
+        <v>0.07072382089581936</v>
       </c>
       <c r="P40" t="n">
-        <v>0.07072382089581933</v>
+        <v>0.08259219276763169</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.08259219276763169</v>
+        <v>0.3378246458606474</v>
       </c>
       <c r="R40" t="n">
-        <v>0.3910837869610322</v>
+        <v>0.5069705032149286</v>
       </c>
       <c r="S40" t="n">
-        <v>0.5069705032149286</v>
+        <v>0.5179407773258387</v>
       </c>
       <c r="T40" t="n">
-        <v>0.5179407773258387</v>
+        <v>0.34265219038496</v>
       </c>
       <c r="U40" t="n">
-        <v>0.34265219038496</v>
+        <v>0.4874686791290066</v>
       </c>
       <c r="V40" t="n">
-        <v>0.4874686791290066</v>
+        <v>0.4040095744996365</v>
       </c>
       <c r="W40" t="n">
-        <v>0.4040095744996365</v>
+        <v>0.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0.03</v>
+        <v>0.05167778476763985</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.05167778476763985</v>
+        <v>0.3060159201919964</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.3060159201919964</v>
+        <v>0.04603407675552353</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.04603407675552353</v>
+        <v>0.04127205983027255</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.04127205983027255</v>
+        <v>-0.03218910984453278</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.03218910984453278</v>
+        <v>0.01024901050654151</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.01024901050654151</v>
+        <v>0.02777948206283074</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.02777948206283074</v>
+        <v>-0.005454491884213056</v>
       </c>
       <c r="AF40" t="n">
-        <v>-0.009207820083935477</v>
+        <v>-0.01951225595678352</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.01951225595678352</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH40" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ40" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM40" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN40" t="n">
-        <v>100</v>
+        <v>266.2564467313324</v>
       </c>
       <c r="AO40" t="n">
-        <v>266.2564467313324</v>
+        <v>0.004393547906404416</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.004393547906404416</v>
-      </c>
-      <c r="AQ40" t="n">
         <v>5.58445992980593</v>
       </c>
     </row>
@@ -5851,105 +5729,102 @@
         <v>0.1694840107822275</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2805314979346968</v>
+        <v>0.05736495020440473</v>
       </c>
       <c r="K41" t="n">
-        <v>0.05783139405686143</v>
+        <v>0.177170348027705</v>
       </c>
       <c r="L41" t="n">
-        <v>0.1729904246625682</v>
+        <v>0.2010895325258091</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1979071195739353</v>
+        <v>0.2411856351790282</v>
       </c>
       <c r="N41" t="n">
-        <v>0.255384458870943</v>
+        <v>0.1730319575690021</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1707130910685935</v>
+        <v>0.235728327771512</v>
       </c>
       <c r="P41" t="n">
-        <v>0.235728327771512</v>
+        <v>0.1000377324664066</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1000377324664065</v>
+        <v>0.3387209248563655</v>
       </c>
       <c r="R41" t="n">
-        <v>0.3862399855513678</v>
+        <v>0.3379371629923227</v>
       </c>
       <c r="S41" t="n">
-        <v>0.3379371629923227</v>
+        <v>0.1458300871202524</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1458300871202524</v>
+        <v>0.3420715296315473</v>
       </c>
       <c r="U41" t="n">
-        <v>0.3420715296315473</v>
+        <v>0.1726069721241738</v>
       </c>
       <c r="V41" t="n">
-        <v>0.1726069721241738</v>
+        <v>0.2796152289578038</v>
       </c>
       <c r="W41" t="n">
-        <v>0.2796152289578038</v>
+        <v>0.06111111111111111</v>
       </c>
       <c r="X41" t="n">
-        <v>0.06111111111111111</v>
+        <v>0.1746479998253042</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1746479998253042</v>
+        <v>0.06302478739381005</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.06302478739381005</v>
+        <v>0.1697394313813524</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.1697394313813524</v>
+        <v>0.05427819884465619</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.05427819884465619</v>
+        <v>-0.09070748387434723</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.09070748387434723</v>
+        <v>0.02919190583745144</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.02919190583745144</v>
+        <v>0.0753928947740745</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.0753928947740745</v>
+        <v>-0.0208382099446062</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.02481618272734552</v>
+        <v>0.08979355894376795</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.08979355894376795</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH41" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ41" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM41" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN41" t="n">
-        <v>100</v>
+        <v>635.1007822918393</v>
       </c>
       <c r="AO41" t="n">
-        <v>635.1007822918393</v>
+        <v>0.01047991793869965</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.01047991793869965</v>
-      </c>
-      <c r="AQ41" t="n">
         <v>6.453783698569845</v>
       </c>
     </row>
@@ -5984,105 +5859,102 @@
         <v>0.306734730401443</v>
       </c>
       <c r="J42" t="n">
-        <v>0.538156155052396</v>
+        <v>0.2252579734414215</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2377721176473618</v>
+        <v>0.2856338358151407</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2919390133642236</v>
+        <v>0.3530528674681963</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3485679625124619</v>
+        <v>0.3285547834597212</v>
       </c>
       <c r="N42" t="n">
-        <v>0.3362494948634881</v>
+        <v>0.2931736741957908</v>
       </c>
       <c r="O42" t="n">
-        <v>0.2888232433728547</v>
+        <v>0.3964802600300886</v>
       </c>
       <c r="P42" t="n">
-        <v>0.3964802600300886</v>
+        <v>0.2903617608507111</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.290361760850711</v>
+        <v>0.278834069739235</v>
       </c>
       <c r="R42" t="n">
-        <v>0.3360900007309864</v>
+        <v>0.4436181966649688</v>
       </c>
       <c r="S42" t="n">
-        <v>0.4436181966649688</v>
+        <v>0.3567397310898089</v>
       </c>
       <c r="T42" t="n">
-        <v>0.3567397310898089</v>
+        <v>0.6167793593258108</v>
       </c>
       <c r="U42" t="n">
-        <v>0.6167793593258108</v>
+        <v>0.2984211181041735</v>
       </c>
       <c r="V42" t="n">
-        <v>0.2984211181041735</v>
+        <v>0.3515195315425074</v>
       </c>
       <c r="W42" t="n">
-        <v>0.3515195315425074</v>
+        <v>0.2722222222222223</v>
       </c>
       <c r="X42" t="n">
-        <v>0.2722222222222223</v>
+        <v>0.3162077297014624</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.3162077297014624</v>
+        <v>0.13349244705589</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.13349244705589</v>
+        <v>0.2340190985341616</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.2340190985341616</v>
+        <v>0.1834846246209429</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.1834846246209429</v>
+        <v>-0.1922961259318508</v>
       </c>
       <c r="AC42" t="n">
-        <v>-0.1922961259318508</v>
+        <v>0.0002273942260509989</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.0002273942260509989</v>
+        <v>0.171052380447292</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.171052380447292</v>
+        <v>0.003378923925822649</v>
       </c>
       <c r="AF42" t="n">
-        <v>-0.01304709455080364</v>
+        <v>0.02145466503142757</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.02145466503142757</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH42" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ42" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM42" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN42" t="n">
-        <v>100</v>
+        <v>1056.680408594453</v>
       </c>
       <c r="AO42" t="n">
-        <v>1056.680408594453</v>
+        <v>0.01743648296186924</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.01743648296186924</v>
-      </c>
-      <c r="AQ42" t="n">
         <v>6.96288758309763</v>
       </c>
     </row>
@@ -6117,105 +5989,102 @@
         <v>0.1021938814397976</v>
       </c>
       <c r="J43" t="n">
-        <v>0.3989797057925368</v>
+        <v>0.09359639319741167</v>
       </c>
       <c r="K43" t="n">
-        <v>0.09199345093305825</v>
+        <v>0.2809115919090762</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2779298333235067</v>
+        <v>0.2615838232592932</v>
       </c>
       <c r="M43" t="n">
-        <v>0.256056030359717</v>
+        <v>0.3121474212859008</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3331868392931687</v>
+        <v>0.2573308050302817</v>
       </c>
       <c r="O43" t="n">
-        <v>0.2560587214351626</v>
+        <v>0.134759389259483</v>
       </c>
       <c r="P43" t="n">
-        <v>0.134759389259483</v>
+        <v>0.1397182511941127</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.1397182511941127</v>
+        <v>0.3600505034117562</v>
       </c>
       <c r="R43" t="n">
-        <v>0.3991197265169932</v>
+        <v>0.4635408841975608</v>
       </c>
       <c r="S43" t="n">
-        <v>0.4635408841975608</v>
+        <v>0.1800222400805816</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1800222400805816</v>
+        <v>0.5058226177194309</v>
       </c>
       <c r="U43" t="n">
-        <v>0.5058226177194309</v>
+        <v>0.119193853925154</v>
       </c>
       <c r="V43" t="n">
-        <v>0.119193853925154</v>
+        <v>0.3038915109448072</v>
       </c>
       <c r="W43" t="n">
-        <v>0.3038915109448072</v>
+        <v>0.2066666666666667</v>
       </c>
       <c r="X43" t="n">
-        <v>0.2066666666666667</v>
+        <v>0.1053412739766418</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1053412739766418</v>
+        <v>0.03223437270433763</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.03223437270433763</v>
+        <v>0.1013895914747767</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.1013895914747767</v>
+        <v>0.08266012307518623</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.08266012307518623</v>
+        <v>-0.04453440304908399</v>
       </c>
       <c r="AC43" t="n">
-        <v>-0.04453440304908399</v>
+        <v>0.04157457700881244</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.04157457700881244</v>
+        <v>0.0399489678531709</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.0399489678531709</v>
+        <v>-0.0269130254985074</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.02067718374917468</v>
+        <v>0.008571611351655406</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.008571611351655406</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH43" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ43" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM43" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN43" t="n">
-        <v>100</v>
+        <v>433.3865980341443</v>
       </c>
       <c r="AO43" t="n">
-        <v>433.3865980341443</v>
+        <v>0.007151394093296809</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.007151394093296809</v>
-      </c>
-      <c r="AQ43" t="n">
         <v>6.071630165767987</v>
       </c>
     </row>
@@ -6250,105 +6119,102 @@
         <v>0.0915700711966</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6254986469115791</v>
+        <v>0.0124226053266774</v>
       </c>
       <c r="K44" t="n">
-        <v>0.012800627185129</v>
+        <v>0.3517799565730474</v>
       </c>
       <c r="L44" t="n">
-        <v>0.3586092338007782</v>
+        <v>0.3730604120208577</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3681355628638203</v>
+        <v>0.3565464980259754</v>
       </c>
       <c r="N44" t="n">
-        <v>0.3646777317617673</v>
+        <v>0.3343648152690269</v>
       </c>
       <c r="O44" t="n">
-        <v>0.3288922177094067</v>
+        <v>0.02502748757149661</v>
       </c>
       <c r="P44" t="n">
-        <v>0.02502748757149661</v>
+        <v>0.05325112861724624</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.05325112861724622</v>
+        <v>0.3413960842836097</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3933963323370602</v>
+        <v>0.4865134985340695</v>
       </c>
       <c r="S44" t="n">
-        <v>0.4865134985340695</v>
+        <v>0.5636389804148151</v>
       </c>
       <c r="T44" t="n">
-        <v>0.5636389804148151</v>
+        <v>0.3267195646066371</v>
       </c>
       <c r="U44" t="n">
-        <v>0.3267195646066371</v>
+        <v>0.798221230201185</v>
       </c>
       <c r="V44" t="n">
-        <v>0.798221230201185</v>
+        <v>0.8453292577684213</v>
       </c>
       <c r="W44" t="n">
-        <v>0.8453292577684213</v>
+        <v>0.1733333333333333</v>
       </c>
       <c r="X44" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.02282575403056498</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.02282575403056498</v>
+        <v>0.3796972848685501</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.3796972848685501</v>
+        <v>0.01401529372001456</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.01401529372001456</v>
+        <v>0.01281200602726846</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.01281200602726846</v>
+        <v>-0.009193653152417195</v>
       </c>
       <c r="AC44" t="n">
-        <v>-0.009193653152417195</v>
+        <v>-0.01755721074547265</v>
       </c>
       <c r="AD44" t="n">
-        <v>-0.01755721074547265</v>
+        <v>0.009030523174687359</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.009030523174687359</v>
+        <v>-0.002278700101378356</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.003054045741028504</v>
+        <v>-0.006283684811464241</v>
       </c>
       <c r="AG44" t="n">
-        <v>-0.006283684811464241</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH44" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ44" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM44" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN44" t="n">
-        <v>100</v>
+        <v>145.1928174783797</v>
       </c>
       <c r="AO44" t="n">
-        <v>145.1928174783797</v>
+        <v>0.00239585409888979</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.00239585409888979</v>
-      </c>
-      <c r="AQ44" t="n">
         <v>4.978062634764849</v>
       </c>
     </row>
@@ -6383,10 +6249,10 @@
         <v>0.3301174108443398</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4770761694831391</v>
+        <v>0.928143635011051</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9780763661509803</v>
+        <v>0.9532967073477324</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -6398,90 +6264,87 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
+        <v>0.8547558437413914</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.8948574719457679</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.3211814018682101</v>
+      </c>
+      <c r="R45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" t="n">
-        <v>0.8547558437413914</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.8948574719457679</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.3897816627653796</v>
-      </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0.5624981150798624</v>
       </c>
       <c r="T45" t="n">
-        <v>0.5624981150798624</v>
+        <v>0.4883436452851982</v>
       </c>
       <c r="U45" t="n">
-        <v>0.4883436452851982</v>
+        <v>0.5514670584225002</v>
       </c>
       <c r="V45" t="n">
-        <v>0.5514670584225002</v>
+        <v>0.2908325850671941</v>
       </c>
       <c r="W45" t="n">
-        <v>0.2908325850671941</v>
+        <v>0.2388888888888889</v>
       </c>
       <c r="X45" t="n">
-        <v>0.2388888888888889</v>
+        <v>0.3073569613522507</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.3073569613522507</v>
+        <v>0.6110986648757819</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.6110986648757819</v>
+        <v>0.5860188765048852</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.5860188765048852</v>
+        <v>0.5705584271634623</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.5705584271634623</v>
+        <v>-0.4610285995427424</v>
       </c>
       <c r="AC45" t="n">
-        <v>-0.4610285995427424</v>
+        <v>0.4763626392451257</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.4763626392451257</v>
+        <v>0.3177277393241646</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.3177277393241646</v>
+        <v>-0.06719284891117148</v>
       </c>
       <c r="AF45" t="n">
-        <v>-0.1201948505968673</v>
+        <v>-0.3383309626399154</v>
       </c>
       <c r="AG45" t="n">
-        <v>-0.3383309626399154</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH45" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ45" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM45" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN45" t="n">
-        <v>100</v>
+        <v>1155.547772631032</v>
       </c>
       <c r="AO45" t="n">
-        <v>1155.547772631032</v>
+        <v>0.01906791200558718</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.01906791200558718</v>
-      </c>
-      <c r="AQ45" t="n">
         <v>7.052329772547417</v>
       </c>
     </row>
@@ -6516,105 +6379,102 @@
         <v>0.1920013283378901</v>
       </c>
       <c r="J46" t="n">
-        <v>0.4786933516097158</v>
+        <v>0.06509102523740259</v>
       </c>
       <c r="K46" t="n">
-        <v>0.06668620445279264</v>
+        <v>0.2388865917540891</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2387074095046538</v>
+        <v>0.2485378646949557</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2453093033505311</v>
+        <v>0.2786014898212415</v>
       </c>
       <c r="N46" t="n">
-        <v>0.2914311678522609</v>
+        <v>0.2246874286787045</v>
       </c>
       <c r="O46" t="n">
-        <v>0.2218383430957597</v>
+        <v>0.1816783426569649</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1816783426569649</v>
+        <v>0.1167440402564721</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1167440402564721</v>
+        <v>0.3228399690206425</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3721048882283634</v>
+        <v>0.40942490449786</v>
       </c>
       <c r="S46" t="n">
-        <v>0.40942490449786</v>
+        <v>0.2433169957534358</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2433169957534358</v>
+        <v>0.6891194735077638</v>
       </c>
       <c r="U46" t="n">
-        <v>0.6891194735077638</v>
+        <v>0.3040842784611432</v>
       </c>
       <c r="V46" t="n">
-        <v>0.3040842784611432</v>
+        <v>0.430595254716499</v>
       </c>
       <c r="W46" t="n">
-        <v>0.430595254716499</v>
+        <v>0.03666666666666667</v>
       </c>
       <c r="X46" t="n">
-        <v>0.03666666666666667</v>
+        <v>0.1944624773454524</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1944624773454524</v>
+        <v>0.1508578526085919</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.1508578526085919</v>
+        <v>0.1019716648889814</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.1019716648889814</v>
+        <v>0.06794868065834438</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.06794868065834438</v>
+        <v>-0.09066563465995134</v>
       </c>
       <c r="AC46" t="n">
-        <v>-0.09066563465995134</v>
+        <v>-0.0121839866955864</v>
       </c>
       <c r="AD46" t="n">
-        <v>-0.0121839866955864</v>
+        <v>0.08213897565283053</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.08213897565283053</v>
+        <v>-0.008048379031123841</v>
       </c>
       <c r="AF46" t="n">
-        <v>-0.01245706372952565</v>
+        <v>0.04356583942777092</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.04356583942777092</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH46" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ46" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM46" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN46" t="n">
-        <v>100</v>
+        <v>441.0544819527353</v>
       </c>
       <c r="AO46" t="n">
-        <v>441.0544819527353</v>
+        <v>0.007277923293812551</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.007277923293812551</v>
-      </c>
-      <c r="AQ46" t="n">
         <v>6.089168409659118</v>
       </c>
     </row>
@@ -6649,105 +6509,102 @@
         <v>0.1487467313801415</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4333472846081809</v>
+        <v>0.01768656467853381</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01879163299541776</v>
+        <v>0.2030655108169831</v>
       </c>
       <c r="L47" t="n">
-        <v>0.202872894827944</v>
+        <v>0.1987531903440971</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1966168081641973</v>
+        <v>0.2458434599297599</v>
       </c>
       <c r="N47" t="n">
-        <v>0.2622992732325173</v>
+        <v>0.1835523511035449</v>
       </c>
       <c r="O47" t="n">
-        <v>0.1832277175989303</v>
+        <v>0.1211897457909047</v>
       </c>
       <c r="P47" t="n">
-        <v>0.1211897457909047</v>
+        <v>0.06313236499153477</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.06313236499153477</v>
+        <v>0.3280540153540136</v>
       </c>
       <c r="R47" t="n">
-        <v>0.3811488796328082</v>
+        <v>0.4062551645507753</v>
       </c>
       <c r="S47" t="n">
-        <v>0.4062551645507752</v>
+        <v>0.4691849618037568</v>
       </c>
       <c r="T47" t="n">
-        <v>0.4691849618037568</v>
+        <v>0.5534092932608206</v>
       </c>
       <c r="U47" t="n">
-        <v>0.5534092932608206</v>
+        <v>0.6422553816132378</v>
       </c>
       <c r="V47" t="n">
-        <v>0.6422553816132378</v>
+        <v>0.4273864045391075</v>
       </c>
       <c r="W47" t="n">
-        <v>0.4273864045391075</v>
+        <v>0.01888888888888889</v>
       </c>
       <c r="X47" t="n">
-        <v>0.01888888888888889</v>
+        <v>0.1204634392846625</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1204634392846625</v>
+        <v>0.3880590933185397</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.3880590933185397</v>
+        <v>0.06387508450367822</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.06387508450367822</v>
+        <v>0.02488078522356041</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.02488078522356041</v>
+        <v>-0.02141890312634018</v>
       </c>
       <c r="AC47" t="n">
-        <v>-0.02141890312634018</v>
+        <v>-0.01267915408216049</v>
       </c>
       <c r="AD47" t="n">
-        <v>-0.01267915408216049</v>
+        <v>0.05687887101115492</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.05687887101115492</v>
+        <v>0.005830096404442268</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.003703194219283925</v>
+        <v>0.04561555936753336</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.04561555936753336</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH47" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ47" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM47" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN47" t="n">
-        <v>100</v>
+        <v>387.2873483935373</v>
       </c>
       <c r="AO47" t="n">
-        <v>387.2873483935373</v>
+        <v>0.006390701669763956</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.006390701669763956</v>
-      </c>
-      <c r="AQ47" t="n">
         <v>5.959166919820198</v>
       </c>
     </row>
@@ -6782,105 +6639,102 @@
         <v>0.06076722331573604</v>
       </c>
       <c r="J48" t="n">
-        <v>0.3181828108052021</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>0.5340638320583172</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5503618575209929</v>
+        <v>0.6353615961968049</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6270481049475094</v>
+        <v>0.5289236480144101</v>
       </c>
       <c r="N48" t="n">
-        <v>0.4999806336247171</v>
+        <v>0.5486812845620131</v>
       </c>
       <c r="O48" t="n">
-        <v>0.5260858003438784</v>
+        <v>0.01421041524078085</v>
       </c>
       <c r="P48" t="n">
-        <v>0.01421041524078086</v>
+        <v>0.04990409430041927</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.04990409430041925</v>
+        <v>0.3413904388415208</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3938303640716613</v>
+        <v>0.4713183549886679</v>
       </c>
       <c r="S48" t="n">
-        <v>0.4713183549886679</v>
+        <v>0.2962380725637529</v>
       </c>
       <c r="T48" t="n">
-        <v>0.2962380725637529</v>
+        <v>0.0447057435055681</v>
       </c>
       <c r="U48" t="n">
-        <v>0.0447057435055681</v>
+        <v>0.4589768002283043</v>
       </c>
       <c r="V48" t="n">
-        <v>0.4589768002283043</v>
+        <v>0.3819076317262547</v>
       </c>
       <c r="W48" t="n">
-        <v>0.3819076317262547</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.001076702738375063</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.001076702738375063</v>
+        <v>0.2571058271498464</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.2571058271498464</v>
+        <v>0.009510544688683523</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.009510544688683523</v>
+        <v>0.0001868339488914382</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.0001868339488914382</v>
+        <v>-0.001372585750811116</v>
       </c>
       <c r="AC48" t="n">
-        <v>-0.001372585750811116</v>
+        <v>-0.007489350776811177</v>
       </c>
       <c r="AD48" t="n">
-        <v>-0.007489350776811177</v>
+        <v>0.002690662810970722</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.002690662810970722</v>
+        <v>-0.0001102402771849444</v>
       </c>
       <c r="AF48" t="n">
-        <v>-0.0005903930743400127</v>
+        <v>0.003542291209441828</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.003542291209441828</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH48" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ48" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM48" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN48" t="n">
-        <v>100</v>
+        <v>30.04780213465726</v>
       </c>
       <c r="AO48" t="n">
-        <v>30.04780213465726</v>
+        <v>0.0004958244571407111</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.0004958244571407111</v>
-      </c>
-      <c r="AQ48" t="n">
         <v>3.402789518028707</v>
       </c>
     </row>
@@ -6915,105 +6769,102 @@
         <v>0.1067639952275133</v>
       </c>
       <c r="J49" t="n">
+        <v>0.007937565485284686</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.268462179680248</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.2690207952817056</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.2890786233371062</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.2457501345517074</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.04481688330030306</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.05587713272716346</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.3376491971725076</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.4572431254560564</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.6016323062417884</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.8161491151655244</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0.5673775575254262</v>
+      </c>
+      <c r="V49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0.007602634284363627</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.2704901543845801</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.2654280918060282</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0.3074409338163255</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.2451329641229873</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0.04481688330030308</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0.05587713272716344</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.3885055467142973</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.4572431254560564</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0.6016323062417884</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0.8161491151655244</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.5673775575254262</v>
-      </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>0.5611111111111111</v>
       </c>
       <c r="X49" t="n">
-        <v>0.5611111111111111</v>
+        <v>0.09611551552688409</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.09611551552688409</v>
+        <v>0.2144665414589867</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.2144665414589867</v>
+        <v>0.02257011189108322</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.02257011189108322</v>
+        <v>0.01575430731050377</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.01575430731050377</v>
+        <v>-0.02375348364538535</v>
       </c>
       <c r="AC49" t="n">
-        <v>-0.02375348364538535</v>
+        <v>-0.009197189632953719</v>
       </c>
       <c r="AD49" t="n">
-        <v>-0.009197189632953719</v>
+        <v>0.01990000211364723</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.01990000211364723</v>
+        <v>-0.003046202364150849</v>
       </c>
       <c r="AF49" t="n">
-        <v>-0.003867078732887797</v>
+        <v>0.01264407214773655</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.01264407214773655</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH49" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ49" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM49" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN49" t="n">
-        <v>100</v>
+        <v>231.3400427373124</v>
       </c>
       <c r="AO49" t="n">
-        <v>231.3400427373124</v>
+        <v>0.003817385730613446</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.003817385730613446</v>
-      </c>
-      <c r="AQ49" t="n">
         <v>5.44388867460534</v>
       </c>
     </row>
@@ -7048,105 +6899,102 @@
         <v>0.0686090373383727</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5054936546682156</v>
+        <v>0.01219580399284818</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01182462277322826</v>
+        <v>0.3788695124995178</v>
       </c>
       <c r="L50" t="n">
-        <v>0.3862613489018079</v>
+        <v>0.4141795580339642</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4083315788466247</v>
+        <v>0.3936244512981265</v>
       </c>
       <c r="N50" t="n">
-        <v>0.3924860041977052</v>
+        <v>0.371491360527698</v>
       </c>
       <c r="O50" t="n">
-        <v>0.3617597894419622</v>
+        <v>0.03879307573970747</v>
       </c>
       <c r="P50" t="n">
-        <v>0.03879307573970747</v>
+        <v>0.05614395569306288</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.05614395569306287</v>
+        <v>0.3438179530208731</v>
       </c>
       <c r="R50" t="n">
-        <v>0.3941488704830005</v>
+        <v>0.4668970953311947</v>
       </c>
       <c r="S50" t="n">
-        <v>0.4668970953311947</v>
+        <v>0.307885215376515</v>
       </c>
       <c r="T50" t="n">
-        <v>0.307885215376515</v>
+        <v>0.5595770049164974</v>
       </c>
       <c r="U50" t="n">
-        <v>0.5595770049164974</v>
+        <v>0.4557762179652265</v>
       </c>
       <c r="V50" t="n">
-        <v>0.4557762179652265</v>
+        <v>0.5002758493993801</v>
       </c>
       <c r="W50" t="n">
-        <v>0.5002758493993801</v>
+        <v>0.08222222222222222</v>
       </c>
       <c r="X50" t="n">
-        <v>0.08222222222222222</v>
+        <v>0.04522604171022519</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.04522604171022519</v>
+        <v>0.2182581310324081</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.2182581310324081</v>
+        <v>0.02111718603623166</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.02111718603623166</v>
+        <v>0.01477597828036135</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.01477597828036135</v>
+        <v>-0.008799648376315179</v>
       </c>
       <c r="AC50" t="n">
-        <v>-0.008799648376315179</v>
+        <v>0.001327287295643126</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.001327287295643126</v>
+        <v>0.01628830313361964</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.01628830313361964</v>
+        <v>-0.00424468151048282</v>
       </c>
       <c r="AF50" t="n">
-        <v>-0.003598976958167983</v>
+        <v>0.006401309371838694</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.006401309371838694</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH50" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ50" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM50" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN50" t="n">
-        <v>100</v>
+        <v>110.6631027970114</v>
       </c>
       <c r="AO50" t="n">
-        <v>110.6631027970114</v>
+        <v>0.001826072756467876</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.001826072756467876</v>
-      </c>
-      <c r="AQ50" t="n">
         <v>4.706490476088367</v>
       </c>
     </row>
@@ -7181,105 +7029,102 @@
         <v>0.1221848884441112</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5127364187808966</v>
+        <v>0.0272408846723942</v>
       </c>
       <c r="K51" t="n">
-        <v>0.02619025496978723</v>
+        <v>0.303244589262894</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3052956060557226</v>
+        <v>0.3073700160593162</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3024270517234139</v>
+        <v>0.3417582298784445</v>
       </c>
       <c r="N51" t="n">
-        <v>0.3531700005119936</v>
+        <v>0.2911262046632599</v>
       </c>
       <c r="O51" t="n">
-        <v>0.2872225491001896</v>
+        <v>0.07020303218747889</v>
       </c>
       <c r="P51" t="n">
-        <v>0.07020303218747889</v>
+        <v>0.07119640431390577</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.07119640431390575</v>
+        <v>0.3476750983899713</v>
       </c>
       <c r="R51" t="n">
-        <v>0.3949036573732944</v>
+        <v>0.4521415197890518</v>
       </c>
       <c r="S51" t="n">
-        <v>0.4521415197890517</v>
+        <v>0.2710702158255196</v>
       </c>
       <c r="T51" t="n">
-        <v>0.2710702158255196</v>
+        <v>0.7134791973550593</v>
       </c>
       <c r="U51" t="n">
-        <v>0.7134791973550593</v>
+        <v>0.3669971542074126</v>
       </c>
       <c r="V51" t="n">
-        <v>0.3669971542074126</v>
+        <v>0.3747732980360632</v>
       </c>
       <c r="W51" t="n">
-        <v>0.3747732980360632</v>
+        <v>0.1566666666666667</v>
       </c>
       <c r="X51" t="n">
-        <v>0.1566666666666667</v>
+        <v>0.1175584619408706</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1175584619408706</v>
+        <v>0.1799549254520934</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.1799549254520934</v>
+        <v>0.03912951335623666</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.03912951335623666</v>
+        <v>0.02913487495196995</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.02913487495196995</v>
+        <v>-0.03687378842779681</v>
       </c>
       <c r="AC51" t="n">
-        <v>-0.03687378842779681</v>
+        <v>0.03948412246563046</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.03948412246563046</v>
+        <v>0.03118852541845921</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.03118852541845921</v>
+        <v>-0.01488537965273628</v>
       </c>
       <c r="AF51" t="n">
-        <v>-0.01427770299693747</v>
+        <v>0.01594303768908389</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.01594303768908389</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH51" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ51" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM51" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN51" t="n">
-        <v>100</v>
+        <v>247.3887371163211</v>
       </c>
       <c r="AO51" t="n">
-        <v>247.3887371163211</v>
+        <v>0.004082208267138043</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.004082208267138043</v>
-      </c>
-      <c r="AQ51" t="n">
         <v>5.510960933927433</v>
       </c>
     </row>
@@ -7314,40 +7159,40 @@
         <v>0.04648025130781008</v>
       </c>
       <c r="J52" t="n">
-        <v>0.08896416625807346</v>
+        <v>0.005191918856012641</v>
       </c>
       <c r="K52" t="n">
-        <v>0.006312797055932696</v>
+        <v>0.2360521602645237</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2381736346885583</v>
+        <v>0.25086361073666</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2486047014816639</v>
+        <v>0.235255172177686</v>
       </c>
       <c r="N52" t="n">
-        <v>0.2508261291446566</v>
+        <v>0.2068393031041845</v>
       </c>
       <c r="O52" t="n">
-        <v>0.2049846223784684</v>
+        <v>0.1165398610274509</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1165398610274509</v>
+        <v>0.04757007336992406</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.04757007336992405</v>
+        <v>0.3277597673652143</v>
       </c>
       <c r="R52" t="n">
-        <v>0.3821917427814498</v>
+        <v>0.3972264019870717</v>
       </c>
       <c r="S52" t="n">
-        <v>0.3972264019870716</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>0.2402417925237061</v>
       </c>
       <c r="U52" t="n">
-        <v>0.2402417925237061</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
@@ -7356,63 +7201,60 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>0.04805042516206844</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.04805042516206844</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>0.09187721007376878</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.09187721007376878</v>
+        <v>0.01397732073986392</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.01397732073986392</v>
+        <v>-0.07930400905856461</v>
       </c>
       <c r="AC52" t="n">
-        <v>-0.07930400905856461</v>
+        <v>-0.0903584565237078</v>
       </c>
       <c r="AD52" t="n">
-        <v>-0.0903584565237078</v>
+        <v>0.03032146434416024</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.03032146434416024</v>
+        <v>-0.009239203619983625</v>
       </c>
       <c r="AF52" t="n">
-        <v>-0.01751509806377641</v>
+        <v>0.05145403033586149</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.05145403033586149</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH52" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ52" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK52" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM52" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN52" t="n">
-        <v>100</v>
+        <v>253.4984852842852</v>
       </c>
       <c r="AO52" t="n">
-        <v>253.4984852842852</v>
+        <v>0.00418302637540005</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.00418302637540005</v>
-      </c>
-      <c r="AQ52" t="n">
         <v>5.535357847803466</v>
       </c>
     </row>
@@ -7447,105 +7289,102 @@
         <v>0.1015021960563819</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5132931295103672</v>
+        <v>0.06263642942043003</v>
       </c>
       <c r="K53" t="n">
-        <v>0.06546316549364463</v>
+        <v>0.2423505753028637</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2438275268357347</v>
+        <v>0.1878698642936773</v>
       </c>
       <c r="M53" t="n">
-        <v>0.1852788579838525</v>
+        <v>0.27163060098272</v>
       </c>
       <c r="N53" t="n">
-        <v>0.3050904608969898</v>
+        <v>0.2048746859102114</v>
       </c>
       <c r="O53" t="n">
-        <v>0.2120730211778927</v>
+        <v>0.07521126532302679</v>
       </c>
       <c r="P53" t="n">
-        <v>0.07521126532302679</v>
+        <v>0.08680611110935831</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.08680611110935829</v>
+        <v>0.347310637046079</v>
       </c>
       <c r="R53" t="n">
-        <v>0.3996141304017544</v>
+        <v>0.5155570019503907</v>
       </c>
       <c r="S53" t="n">
-        <v>0.5155570019503907</v>
+        <v>0.6911858753565933</v>
       </c>
       <c r="T53" t="n">
-        <v>0.6911858753565933</v>
+        <v>0.2953783481159613</v>
       </c>
       <c r="U53" t="n">
-        <v>0.2953783481159613</v>
+        <v>0.9507781590909488</v>
       </c>
       <c r="V53" t="n">
-        <v>0.9507781590909488</v>
+        <v>0.820236380242664</v>
       </c>
       <c r="W53" t="n">
-        <v>0.820236380242664</v>
+        <v>0.02555555555555556</v>
       </c>
       <c r="X53" t="n">
-        <v>0.02555555555555556</v>
+        <v>0.06246867838639193</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.06246867838639193</v>
+        <v>0.3424453758783212</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.3424453758783212</v>
+        <v>0.04459064513948564</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.04459064513948564</v>
+        <v>0.04391400375924345</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.04391400375924345</v>
+        <v>-0.0226787235150534</v>
       </c>
       <c r="AC53" t="n">
-        <v>-0.0226787235150534</v>
+        <v>0.02708700996495812</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.02708700996495812</v>
+        <v>0.03214948550430929</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.03214948550430929</v>
+        <v>-0.0109089894822208</v>
       </c>
       <c r="AF53" t="n">
-        <v>-0.01352093900714451</v>
+        <v>-0.02506473595975934</v>
       </c>
       <c r="AG53" t="n">
-        <v>-0.02506473595975934</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH53" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ53" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK53" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM53" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN53" t="n">
-        <v>100</v>
+        <v>388.6414664631744</v>
       </c>
       <c r="AO53" t="n">
-        <v>388.6414664631744</v>
+        <v>0.006413046227737726</v>
       </c>
       <c r="AP53" t="n">
-        <v>0.006413046227737726</v>
-      </c>
-      <c r="AQ53" t="n">
         <v>5.962657238566974</v>
       </c>
     </row>
@@ -7580,105 +7419,102 @@
         <v>0.2505882972645384</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5641509131237906</v>
+        <v>0.05037425841559628</v>
       </c>
       <c r="K54" t="n">
-        <v>0.05587101276168333</v>
+        <v>0.1872395685478882</v>
       </c>
       <c r="L54" t="n">
-        <v>0.1894662942222624</v>
+        <v>0.2329075558263879</v>
       </c>
       <c r="M54" t="n">
-        <v>0.2313840358637151</v>
+        <v>0.1970436168397286</v>
       </c>
       <c r="N54" t="n">
-        <v>0.2059528455075887</v>
+        <v>0.1683849230036981</v>
       </c>
       <c r="O54" t="n">
-        <v>0.1643972047891849</v>
+        <v>0.2425535453330726</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2425535453330726</v>
+        <v>0.111926754765155</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.111926754765155</v>
+        <v>0.2806890052540924</v>
       </c>
       <c r="R54" t="n">
-        <v>0.3403030365211646</v>
+        <v>0.3607300534975069</v>
       </c>
       <c r="S54" t="n">
-        <v>0.3607300534975069</v>
+        <v>0.2900716158874725</v>
       </c>
       <c r="T54" t="n">
-        <v>0.2900716158874725</v>
+        <v>0.7041185179894941</v>
       </c>
       <c r="U54" t="n">
-        <v>0.7041185179894941</v>
+        <v>0.3600175303595512</v>
       </c>
       <c r="V54" t="n">
-        <v>0.3600175303595512</v>
+        <v>0.3536459196008842</v>
       </c>
       <c r="W54" t="n">
-        <v>0.3536459196008842</v>
+        <v>0.2577777777777778</v>
       </c>
       <c r="X54" t="n">
-        <v>0.2577777777777778</v>
+        <v>0.2530631016929431</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.2530631016929431</v>
+        <v>0.2105246538678196</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.2105246538678196</v>
+        <v>0.1286420958960197</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.1286420958960197</v>
+        <v>0.06808771132483643</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.06808771132483643</v>
+        <v>-0.1281998669288909</v>
       </c>
       <c r="AC54" t="n">
-        <v>-0.1281998669288909</v>
+        <v>-0.1502653461926932</v>
       </c>
       <c r="AD54" t="n">
-        <v>-0.1502653461926932</v>
+        <v>0.1148216439046681</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.1148216439046681</v>
+        <v>0.01698793415749351</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.002940494869556345</v>
+        <v>0.07505448162726225</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.07505448162726225</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH54" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ54" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK54" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM54" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN54" t="n">
-        <v>100</v>
+        <v>515.4518292148504</v>
       </c>
       <c r="AO54" t="n">
-        <v>515.4518292148504</v>
+        <v>0.008505567969906858</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.008505567969906858</v>
-      </c>
-      <c r="AQ54" t="n">
         <v>6.245043854308723</v>
       </c>
     </row>
@@ -7713,105 +7549,102 @@
         <v>0.2539434071053177</v>
       </c>
       <c r="J55" t="n">
-        <v>0.342468655088179</v>
+        <v>0.1723817827492499</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1882187298634909</v>
+        <v>0.1477695730282641</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1533484256509779</v>
+        <v>0.2790197131042491</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2747512774568808</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.08834959935720474</v>
       </c>
       <c r="O55" t="n">
-        <v>0.07558154262272404</v>
+        <v>0.6157118308767583</v>
       </c>
       <c r="P55" t="n">
-        <v>0.6157118308767582</v>
+        <v>0.1194300841660211</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.1194300841660211</v>
+        <v>0.3453770307292289</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4156487519944667</v>
+        <v>0.2037851498082547</v>
       </c>
       <c r="S55" t="n">
-        <v>0.2037851498082547</v>
+        <v>0.3133752950272737</v>
       </c>
       <c r="T55" t="n">
-        <v>0.3133752950272737</v>
+        <v>0.1347251541706032</v>
       </c>
       <c r="U55" t="n">
-        <v>0.1347251541706032</v>
+        <v>0.4753641657691908</v>
       </c>
       <c r="V55" t="n">
-        <v>0.4753641657691908</v>
+        <v>0.3970221995003379</v>
       </c>
       <c r="W55" t="n">
-        <v>0.3970221995003379</v>
+        <v>0.26</v>
       </c>
       <c r="X55" t="n">
-        <v>0.26</v>
+        <v>0.2527474298202277</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.2527474298202277</v>
+        <v>0.2717731191365926</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.2717731191365926</v>
+        <v>0.4405678897142913</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.4405678897142913</v>
+        <v>0.07682288619233651</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.07682288619233651</v>
+        <v>-0.2597155728667726</v>
       </c>
       <c r="AC55" t="n">
-        <v>-0.2597155728667726</v>
+        <v>-0.5101867450787266</v>
       </c>
       <c r="AD55" t="n">
-        <v>-0.5101867450787266</v>
+        <v>0.2046128271158935</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.2046128271158935</v>
+        <v>-0.05965142446419319</v>
       </c>
       <c r="AF55" t="n">
-        <v>-0.09946960735973212</v>
+        <v>0.1765432800480369</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.1765432800480369</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH55" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ55" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK55" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM55" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN55" t="n">
-        <v>100</v>
+        <v>1799.693756244028</v>
       </c>
       <c r="AO55" t="n">
-        <v>1799.693756244028</v>
+        <v>0.02969708651934987</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.02969708651934987</v>
-      </c>
-      <c r="AQ55" t="n">
         <v>7.495371793989599</v>
       </c>
     </row>
@@ -7846,105 +7679,102 @@
         <v>0.03299883580813577</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.1442557443239006</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1513878158761139</v>
+        <v>0.1936678759322911</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1933734694896495</v>
+        <v>0.2231037520210457</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2197532745187698</v>
+        <v>0.1512430828525294</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1850197239550371</v>
+        <v>0.1492378630471011</v>
       </c>
       <c r="O56" t="n">
-        <v>0.1532307198686087</v>
+        <v>0.3802447044835606</v>
       </c>
       <c r="P56" t="n">
-        <v>0.3802447044835605</v>
+        <v>0.111541384759202</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.111541384759202</v>
+        <v>0.3699900921212831</v>
       </c>
       <c r="R56" t="n">
-        <v>0.4235211314512527</v>
+        <v>0.356042812156856</v>
       </c>
       <c r="S56" t="n">
-        <v>0.356042812156856</v>
+        <v>0.1086975650744415</v>
       </c>
       <c r="T56" t="n">
-        <v>0.1086975650744415</v>
+        <v>0.0149359379319865</v>
       </c>
       <c r="U56" t="n">
-        <v>0.0149359379319865</v>
+        <v>0.1448096850876939</v>
       </c>
       <c r="V56" t="n">
-        <v>0.1448096850876939</v>
+        <v>0.1214275561293924</v>
       </c>
       <c r="W56" t="n">
-        <v>0.1214275561293924</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>0.02056323384441369</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.02056323384441369</v>
+        <v>0.1073968774684603</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.1073968774684603</v>
+        <v>0.330046728637271</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.330046728637271</v>
+        <v>0.06700770441298946</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.06700770441298946</v>
+        <v>-0.2538966352921019</v>
       </c>
       <c r="AC56" t="n">
-        <v>-0.2538966352921019</v>
+        <v>-0.1141123716619992</v>
       </c>
       <c r="AD56" t="n">
-        <v>-0.1141123716619992</v>
+        <v>0.05952496954552933</v>
       </c>
       <c r="AE56" t="n">
-        <v>0.05952496954552933</v>
+        <v>-0.07749862478962509</v>
       </c>
       <c r="AF56" t="n">
-        <v>-0.1050721839466054</v>
+        <v>0.07808549748307314</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.07808549748307314</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH56" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ56" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK56" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM56" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN56" t="n">
-        <v>100</v>
+        <v>1014.677766584166</v>
       </c>
       <c r="AO56" t="n">
-        <v>1014.677766584166</v>
+        <v>0.01674338943443265</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.01674338943443265</v>
-      </c>
-      <c r="AQ56" t="n">
         <v>6.922326369725542</v>
       </c>
     </row>
@@ -7979,105 +7809,102 @@
         <v>0.05699796832426152</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1839592415502736</v>
+        <v>0.09891823550755639</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1072869072138623</v>
+        <v>0.1365222462705548</v>
       </c>
       <c r="L57" t="n">
-        <v>0.1369319970209936</v>
+        <v>0.1479832905992687</v>
       </c>
       <c r="M57" t="n">
-        <v>0.1462652701588642</v>
+        <v>0.08348875858978798</v>
       </c>
       <c r="N57" t="n">
-        <v>0.1132158577388624</v>
+        <v>0.07864345517702526</v>
       </c>
       <c r="O57" t="n">
-        <v>0.08209043292600487</v>
+        <v>0.3398791053164789</v>
       </c>
       <c r="P57" t="n">
-        <v>0.3398791053164789</v>
+        <v>0.05950444202713696</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.05950444202713696</v>
+        <v>0.3657973523192093</v>
       </c>
       <c r="R57" t="n">
-        <v>0.4268448529109167</v>
+        <v>0.345468045407344</v>
       </c>
       <c r="S57" t="n">
-        <v>0.345468045407344</v>
+        <v>0.3129283238439404</v>
       </c>
       <c r="T57" t="n">
-        <v>0.3129283238439404</v>
+        <v>0.009020347200002408</v>
       </c>
       <c r="U57" t="n">
-        <v>0.009020347200002408</v>
+        <v>0.4492123607035528</v>
       </c>
       <c r="V57" t="n">
-        <v>0.4492123607035528</v>
+        <v>0.444545984234082</v>
       </c>
       <c r="W57" t="n">
-        <v>0.444545984234082</v>
+        <v>0.02444444444444445</v>
       </c>
       <c r="X57" t="n">
-        <v>0.02444444444444445</v>
+        <v>0.02104614257564769</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.02104614257564769</v>
+        <v>0.2212170596558934</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.2212170596558934</v>
+        <v>0.2598132535525026</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.2598132535525026</v>
+        <v>0.03316678071032053</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.03316678071032053</v>
+        <v>-0.1438245788739887</v>
       </c>
       <c r="AC57" t="n">
-        <v>-0.1438245788739887</v>
+        <v>-0.2160121674721138</v>
       </c>
       <c r="AD57" t="n">
-        <v>-0.2160121674721138</v>
+        <v>0.09237053921623062</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.09237053921623062</v>
+        <v>-0.0536358093266775</v>
       </c>
       <c r="AF57" t="n">
-        <v>-0.07654900009829615</v>
+        <v>0.08492369576642034</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.08492369576642034</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH57" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ57" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK57" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM57" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN57" t="n">
-        <v>100</v>
+        <v>1070.536368377464</v>
       </c>
       <c r="AO57" t="n">
-        <v>1070.536368377464</v>
+        <v>0.01766512277075731</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.01766512277075731</v>
-      </c>
-      <c r="AQ57" t="n">
         <v>6.97591508071512</v>
       </c>
     </row>
@@ -8112,105 +7939,102 @@
         <v>0.0613780639918845</v>
       </c>
       <c r="J58" t="n">
-        <v>0.2109593417762431</v>
+        <v>0.01382622998201063</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01459285078312333</v>
+        <v>0.4188678913364022</v>
       </c>
       <c r="L58" t="n">
-        <v>0.4294680258827999</v>
+        <v>0.4631921211469252</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4571997640407851</v>
+        <v>0.4227345942574097</v>
       </c>
       <c r="N58" t="n">
-        <v>0.4186523853563711</v>
+        <v>0.4124260418414648</v>
       </c>
       <c r="O58" t="n">
-        <v>0.4015724909236211</v>
+        <v>0.02389981727454032</v>
       </c>
       <c r="P58" t="n">
-        <v>0.02389981727454032</v>
+        <v>0.05376225960671928</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.05376225960671926</v>
+        <v>0.3422466500262616</v>
       </c>
       <c r="R58" t="n">
-        <v>0.3949788090012022</v>
+        <v>0.4895973986071274</v>
       </c>
       <c r="S58" t="n">
-        <v>0.4895973986071274</v>
+        <v>0.2794963771226884</v>
       </c>
       <c r="T58" t="n">
-        <v>0.2794963771226884</v>
+        <v>0.03058853366327968</v>
       </c>
       <c r="U58" t="n">
-        <v>0.03058853366327968</v>
+        <v>0.3935823019207009</v>
       </c>
       <c r="V58" t="n">
-        <v>0.3935823019207009</v>
+        <v>0.2330256064992975</v>
       </c>
       <c r="W58" t="n">
-        <v>0.2330256064992975</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>0.00229394221554772</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.00229394221554772</v>
+        <v>0.2594054748429906</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.2594054748429906</v>
+        <v>0.01870649349105824</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.01870649349105824</v>
+        <v>0.01236841593042687</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.01236841593042687</v>
+        <v>-0.01068570536964703</v>
       </c>
       <c r="AC58" t="n">
-        <v>-0.01068570536964703</v>
+        <v>-0.008979685165807131</v>
       </c>
       <c r="AD58" t="n">
-        <v>-0.008979685165807131</v>
+        <v>0.006919731104164557</v>
       </c>
       <c r="AE58" t="n">
-        <v>0.006919731104164557</v>
+        <v>-0.003415629880049712</v>
       </c>
       <c r="AF58" t="n">
-        <v>-0.005041072978767908</v>
+        <v>-0.008277896190790557</v>
       </c>
       <c r="AG58" t="n">
-        <v>-0.008277896190790557</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH58" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ58" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK58" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM58" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN58" t="n">
-        <v>100</v>
+        <v>72.20022597511287</v>
       </c>
       <c r="AO58" t="n">
-        <v>72.20022597511287</v>
+        <v>0.001191389562841161</v>
       </c>
       <c r="AP58" t="n">
-        <v>0.001191389562841161</v>
-      </c>
-      <c r="AQ58" t="n">
         <v>4.279443175743092</v>
       </c>
     </row>
@@ -8245,105 +8069,102 @@
         <v>0.02548846226829396</v>
       </c>
       <c r="J59" t="n">
-        <v>0.08754425954433386</v>
+        <v>0.1837823278611346</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1926660652087183</v>
+        <v>0.3688368283897112</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3774242545712791</v>
+        <v>0.2978898243203298</v>
       </c>
       <c r="M59" t="n">
-        <v>0.2938591359545035</v>
+        <v>0.3595666735266591</v>
       </c>
       <c r="N59" t="n">
-        <v>0.3987225859166605</v>
+        <v>0.3191330225073997</v>
       </c>
       <c r="O59" t="n">
-        <v>0.328382483170194</v>
+        <v>0.145286884271392</v>
       </c>
       <c r="P59" t="n">
-        <v>0.145286884271392</v>
+        <v>0.1866744001297166</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1866744001297166</v>
+        <v>0.3466561447193072</v>
       </c>
       <c r="R59" t="n">
-        <v>0.4000284633783942</v>
+        <v>0.6326355880901643</v>
       </c>
       <c r="S59" t="n">
-        <v>0.6326355880901644</v>
+        <v>0.157061467376123</v>
       </c>
       <c r="T59" t="n">
-        <v>0.157061467376123</v>
+        <v>0.05887555227910403</v>
       </c>
       <c r="U59" t="n">
-        <v>0.05887555227910403</v>
+        <v>0.1545357411480393</v>
       </c>
       <c r="V59" t="n">
-        <v>0.1545357411480393</v>
+        <v>0.1953529903233083</v>
       </c>
       <c r="W59" t="n">
-        <v>0.1953529903233083</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>0.01614010501871914</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.01614010501871914</v>
+        <v>0.0819334855215352</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.0819334855215352</v>
+        <v>0.1220708105436853</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.1220708105436853</v>
+        <v>0.1146772128203432</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.1146772128203432</v>
+        <v>-0.09618309107904044</v>
       </c>
       <c r="AC59" t="n">
-        <v>-0.09618309107904044</v>
+        <v>0.04330398462220784</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.04330398462220784</v>
+        <v>0.02545999485476377</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.02545999485476377</v>
+        <v>-0.02841794116886209</v>
       </c>
       <c r="AF59" t="n">
-        <v>-0.0385566981465825</v>
+        <v>-0.1007738845132877</v>
       </c>
       <c r="AG59" t="n">
-        <v>-0.1007738845132877</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH59" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ59" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK59" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM59" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN59" t="n">
-        <v>100</v>
+        <v>394.7412976631867</v>
       </c>
       <c r="AO59" t="n">
-        <v>394.7412976631867</v>
+        <v>0.006513700694238877</v>
       </c>
       <c r="AP59" t="n">
-        <v>0.006513700694238877</v>
-      </c>
-      <c r="AQ59" t="n">
         <v>5.978230607707665</v>
       </c>
     </row>
@@ -8378,105 +8199,102 @@
         <v>0.07593329224056376</v>
       </c>
       <c r="J60" t="n">
-        <v>0.43099060225146</v>
+        <v>0.02214483128054311</v>
       </c>
       <c r="K60" t="n">
-        <v>0.02325076028657164</v>
+        <v>0.3496673999461191</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3567103628751925</v>
+        <v>0.3608901096289199</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3561548685664022</v>
+        <v>0.3536063004660277</v>
       </c>
       <c r="N60" t="n">
-        <v>0.363073438687507</v>
+        <v>0.3287543389322804</v>
       </c>
       <c r="O60" t="n">
-        <v>0.3240966751992451</v>
+        <v>0.03673964802445982</v>
       </c>
       <c r="P60" t="n">
-        <v>0.03673964802445983</v>
+        <v>0.05574769723744735</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.05574769723744734</v>
+        <v>0.3448111492909999</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3974436054917919</v>
+        <v>0.4918713691661808</v>
       </c>
       <c r="S60" t="n">
-        <v>0.4918713691661808</v>
+        <v>0.467191900992376</v>
       </c>
       <c r="T60" t="n">
-        <v>0.467191900992376</v>
+        <v>0.1106022615169996</v>
       </c>
       <c r="U60" t="n">
-        <v>0.1106022615169996</v>
+        <v>0.7065420957093491</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7065420957093491</v>
+        <v>0.7173561674594012</v>
       </c>
       <c r="W60" t="n">
-        <v>0.7173561674594012</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>0.01209610478414366</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.01209610478414366</v>
+        <v>0.3187081138260311</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.3187081138260311</v>
+        <v>0.02482099039204903</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.02482099039204903</v>
+        <v>0.01690487555707442</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.01690487555707442</v>
+        <v>-0.01365888291068689</v>
       </c>
       <c r="AC60" t="n">
-        <v>-0.01365888291068689</v>
+        <v>-0.02021755336909394</v>
       </c>
       <c r="AD60" t="n">
-        <v>-0.02021755336909394</v>
+        <v>0.0134412288636973</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.0134412288636973</v>
+        <v>-0.006405846779283684</v>
       </c>
       <c r="AF60" t="n">
-        <v>-0.008353858105740557</v>
+        <v>-0.009748364707178325</v>
       </c>
       <c r="AG60" t="n">
-        <v>-0.009748364707178325</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH60" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ60" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK60" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM60" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN60" t="n">
-        <v>100</v>
+        <v>127.9639877008855</v>
       </c>
       <c r="AO60" t="n">
-        <v>127.9639877008855</v>
+        <v>0.002111557925302343</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.002111557925302343</v>
-      </c>
-      <c r="AQ60" t="n">
         <v>4.85174887824755</v>
       </c>
     </row>
@@ -8511,105 +8329,102 @@
         <v>0.05604947950102564</v>
       </c>
       <c r="J61" t="n">
-        <v>0.3317194490181325</v>
+        <v>0.02144914396966553</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0227632047748552</v>
+        <v>0.3197704244775977</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3255569877438948</v>
+        <v>0.321739280851706</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3177447188986979</v>
+        <v>0.3157876150175261</v>
       </c>
       <c r="N61" t="n">
-        <v>0.3304068903682705</v>
+        <v>0.2909076420355646</v>
       </c>
       <c r="O61" t="n">
-        <v>0.2884785646081588</v>
+        <v>0.04496212871214113</v>
       </c>
       <c r="P61" t="n">
-        <v>0.04496212871214112</v>
+        <v>0.05449374904598058</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.05449374904598057</v>
+        <v>0.3427836344430502</v>
       </c>
       <c r="R61" t="n">
-        <v>0.3959588598910436</v>
+        <v>0.485285866746701</v>
       </c>
       <c r="S61" t="n">
-        <v>0.485285866746701</v>
+        <v>0.3831734503243074</v>
       </c>
       <c r="T61" t="n">
-        <v>0.3831734503243074</v>
+        <v>0.1418424846472857</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1418424846472857</v>
+        <v>0.4120461305617242</v>
       </c>
       <c r="V61" t="n">
-        <v>0.4120461305617242</v>
+        <v>0.456264878068437</v>
       </c>
       <c r="W61" t="n">
-        <v>0.456264878068437</v>
+        <v>0.07333333333333333</v>
       </c>
       <c r="X61" t="n">
-        <v>0.07333333333333333</v>
+        <v>0.009900408630260898</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.009900408630260898</v>
+        <v>0.2310585979627782</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.2310585979627782</v>
+        <v>0.03412961514864436</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.03412961514864436</v>
+        <v>0.01830692940407982</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.01830692940407982</v>
+        <v>-0.02694169776187818</v>
       </c>
       <c r="AC61" t="n">
-        <v>-0.02694169776187818</v>
+        <v>-0.04795332575981778</v>
       </c>
       <c r="AD61" t="n">
-        <v>-0.04795332575981778</v>
+        <v>0.01449149015884511</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.01449149015884511</v>
+        <v>-0.008234026862855594</v>
       </c>
       <c r="AF61" t="n">
-        <v>-0.01173887055783855</v>
+        <v>-0.005489833771548547</v>
       </c>
       <c r="AG61" t="n">
-        <v>-0.005489833771548547</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH61" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ61" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK61" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM61" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN61" t="n">
-        <v>100</v>
+        <v>156.5088497175263</v>
       </c>
       <c r="AO61" t="n">
-        <v>156.5088497175263</v>
+        <v>0.002582582083745965</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.002582582083745965</v>
-      </c>
-      <c r="AQ61" t="n">
         <v>5.053112556097269</v>
       </c>
     </row>
@@ -8644,105 +8459,102 @@
         <v>0.06310697026590414</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3200657234101854</v>
+        <v>0.01279703889960636</v>
       </c>
       <c r="K62" t="n">
-        <v>0.01366700006784611</v>
+        <v>0.4449838259858848</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4570770776682223</v>
+        <v>0.5001540905059367</v>
       </c>
       <c r="M62" t="n">
-        <v>0.4938151248687246</v>
+        <v>0.452471774707192</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4426311541674959</v>
+        <v>0.4449833794839311</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4317256526909123</v>
+        <v>0.02337681764920436</v>
       </c>
       <c r="P62" t="n">
-        <v>0.02337681764920436</v>
+        <v>0.05489035078421121</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.05489035078421119</v>
+        <v>0.3388171704219033</v>
       </c>
       <c r="R62" t="n">
-        <v>0.3918900406318399</v>
+        <v>0.4899889565139167</v>
       </c>
       <c r="S62" t="n">
-        <v>0.4899889565139167</v>
+        <v>0.327066432427266</v>
       </c>
       <c r="T62" t="n">
-        <v>0.327066432427266</v>
+        <v>0.1822899231686168</v>
       </c>
       <c r="U62" t="n">
-        <v>0.1822899231686168</v>
+        <v>0.4867136610698435</v>
       </c>
       <c r="V62" t="n">
-        <v>0.4867136610698435</v>
+        <v>0.374601885732131</v>
       </c>
       <c r="W62" t="n">
-        <v>0.374601885732131</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>0.008469209475348545</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.008469209475348545</v>
+        <v>0.263643669416235</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.263643669416235</v>
+        <v>0.0140266688154771</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.0140266688154771</v>
+        <v>0.01271478158936705</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.01271478158936705</v>
+        <v>-0.004898459072688223</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.004898459072688223</v>
+        <v>0.001378675710972751</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.001378675710972751</v>
+        <v>0.007967442147638379</v>
       </c>
       <c r="AE62" t="n">
-        <v>0.007967442147638379</v>
+        <v>0.0011342192007438</v>
       </c>
       <c r="AF62" t="n">
-        <v>-0.0001006544914652207</v>
+        <v>-0.008531098050411856</v>
       </c>
       <c r="AG62" t="n">
-        <v>-0.008531098050411856</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH62" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ62" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK62" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM62" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN62" t="n">
-        <v>100</v>
+        <v>60.13049925839204</v>
       </c>
       <c r="AO62" t="n">
-        <v>60.13049925839204</v>
+        <v>0.0009922247230856321</v>
       </c>
       <c r="AP62" t="n">
-        <v>0.0009922247230856321</v>
-      </c>
-      <c r="AQ62" t="n">
         <v>4.096517188000411</v>
       </c>
     </row>
@@ -8777,105 +8589,102 @@
         <v>0.0488720409493843</v>
       </c>
       <c r="J63" t="n">
-        <v>0.221891536998549</v>
+        <v>0.04735704308227625</v>
       </c>
       <c r="K63" t="n">
-        <v>0.04975816904726126</v>
+        <v>0.3794793146420848</v>
       </c>
       <c r="L63" t="n">
-        <v>0.3882176841884978</v>
+        <v>0.3806585575383375</v>
       </c>
       <c r="M63" t="n">
-        <v>0.3758289054678851</v>
+        <v>0.3849793761531596</v>
       </c>
       <c r="N63" t="n">
-        <v>0.3950115630162632</v>
+        <v>0.358135792404982</v>
       </c>
       <c r="O63" t="n">
-        <v>0.3540878557213085</v>
+        <v>0.04497014249802566</v>
       </c>
       <c r="P63" t="n">
-        <v>0.04497014249802565</v>
+        <v>0.07616463515891099</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.07616463515891099</v>
+        <v>0.3413785287620172</v>
       </c>
       <c r="R63" t="n">
-        <v>0.3943117148931226</v>
+        <v>0.5262538759637436</v>
       </c>
       <c r="S63" t="n">
-        <v>0.5262538759637436</v>
+        <v>0.2287954107582578</v>
       </c>
       <c r="T63" t="n">
-        <v>0.2287954107582578</v>
+        <v>0.1065485903316251</v>
       </c>
       <c r="U63" t="n">
-        <v>0.1065485903316251</v>
+        <v>0.3147645377478576</v>
       </c>
       <c r="V63" t="n">
-        <v>0.3147645377478576</v>
+        <v>0.2989096197275781</v>
       </c>
       <c r="W63" t="n">
-        <v>0.2989096197275781</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>0.008770603013077685</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.008770603013077685</v>
+        <v>0.2003587027477499</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.2003587027477499</v>
+        <v>0.03682948764360038</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.03682948764360038</v>
+        <v>0.03662464975205414</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.03662464975205414</v>
+        <v>-0.02306821221721244</v>
       </c>
       <c r="AC63" t="n">
-        <v>-0.02306821221721244</v>
+        <v>-0.004744877484451731</v>
       </c>
       <c r="AD63" t="n">
-        <v>-0.004744877484451731</v>
+        <v>0.01243765136264164</v>
       </c>
       <c r="AE63" t="n">
-        <v>0.01243765136264164</v>
+        <v>-0.006021671049115598</v>
       </c>
       <c r="AF63" t="n">
-        <v>-0.008881263020780319</v>
+        <v>-0.03198189519815742</v>
       </c>
       <c r="AG63" t="n">
-        <v>-0.03198189519815742</v>
+        <v>27091.46906470115</v>
       </c>
       <c r="AH63" t="n">
-        <v>27091.46906470115</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>26.94364154622431</v>
       </c>
       <c r="AJ63" t="n">
-        <v>26.94364154622431</v>
+        <v>0.3176552714712887</v>
       </c>
       <c r="AK63" t="n">
-        <v>0.3176552714712887</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>17.03498506003199</v>
       </c>
       <c r="AM63" t="n">
-        <v>16.3874523430173</v>
+        <v>100</v>
       </c>
       <c r="AN63" t="n">
-        <v>100</v>
+        <v>109.5564105553478</v>
       </c>
       <c r="AO63" t="n">
-        <v>109.5564105553478</v>
+        <v>0.001807811018804482</v>
       </c>
       <c r="AP63" t="n">
-        <v>0.001807811018804482</v>
-      </c>
-      <c r="AQ63" t="n">
         <v>4.696439581493702</v>
       </c>
     </row>
